--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -4669,7 +4669,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -4689,7 +4689,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>2.75</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 29 days</v>
+        <v>15-29 days</v>
       </c>
       <c r="B3">
         <v>2.75</v>
@@ -4711,73 +4711,73 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 days to 45 days</v>
+        <v>30-45 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 60 days</v>
+        <v>46-60 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days to 89 days</v>
+        <v>61-89 days</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>90 days to less than 6 months</v>
+        <v>90 days &lt;= 6 months</v>
       </c>
       <c r="B7">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>6 months 1 day to 9 months</v>
+        <v>6 months 1 day &lt;=9 months</v>
       </c>
       <c r="B8">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>6.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>9 months 1 day to less than 1 year</v>
+        <v>9 months 1 day to &lt; 1 Year</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C9">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year to less than 15 Months</v>
+        <v>1 Year to &lt; 15 months</v>
       </c>
       <c r="B10">
         <v>6.25</v>
@@ -4788,73 +4788,117 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>15 Months to less than 18 Months</v>
+        <v>15 months to &lt; 18 months</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 Months to less than 21 Months</v>
+        <v>18 months to &lt; 21 months</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>21 Months to 2 Years</v>
+        <v>21 months to 2 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2 Years 1 day to 3 Years</v>
+        <v>2 Years 1 day to &lt; 2 Year 11 Months</v>
       </c>
       <c r="B14">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3 Years 1 day to 5 Years</v>
+        <v>2 Years 11 Months (35 months)</v>
       </c>
       <c r="B15">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
+        <v>2 Years 11 Months 1 day &lt;= 3 Year</v>
+      </c>
+      <c r="B16">
+        <v>6.45</v>
+      </c>
+      <c r="C16">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 Years 1 day to &lt; 4 Years 7 Months</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 Year 7 Months (55 months)</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>4 Year 7 Months 1 day &lt;=5 Years</v>
+      </c>
+      <c r="B19">
+        <v>6.4</v>
+      </c>
+      <c r="C19">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>5 Years 1 day to 10 Years</v>
       </c>
-      <c r="B16">
-        <v>6.4</v>
-      </c>
-      <c r="C16">
-        <v>6.9</v>
+      <c r="B20">
+        <v>6.15</v>
+      </c>
+      <c r="C20">
+        <v>6.65</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -19,18 +19,19 @@
     <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
-    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
-    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
-    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
-    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="South Indian Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
+    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
+    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
+    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
+    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
+    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
   </sheets>
 </workbook>
 </file>
@@ -1949,6 +1950,242 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2106,7 +2343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -2305,198 +2542,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 30 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 179 days</v>
-      </c>
-      <c r="B6">
-        <v>4.25</v>
-      </c>
-      <c r="C6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>180 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.3</v>
-      </c>
-      <c r="C11">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>450 days</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2717,7 +2762,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2737,43 +2782,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 30 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2781,95 +2826,128 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>91 days to 179 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>211 days to 269 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>270 days to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>450 days</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2896,24 +2974,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2921,109 +2999,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -3034,6 +3112,165 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -3248,7 +3485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -3436,165 +3673,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3621,134 +3699,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3760,7 +3838,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3780,62 +3858,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
         <v>7.25</v>
       </c>
-      <c r="C6">
-        <v>7.5</v>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3862,57 +4017,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2 years</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3 years</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4 years</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5 years</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -3923,6 +4078,88 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -19,19 +19,18 @@
     <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="South Indian Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Canara Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of Baroda" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of India" sheetId="20" r:id="rId20"/>
-    <sheet name="Bank of Maharashtra" sheetId="21" r:id="rId21"/>
-    <sheet name="RBL Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="IDBI Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Indian Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="Central Bank of India" sheetId="25" r:id="rId25"/>
-    <sheet name="Bandhan Bank" sheetId="26" r:id="rId26"/>
-    <sheet name="PNB Housing Finance" sheetId="27" r:id="rId27"/>
-    <sheet name="KTDFC" sheetId="28" r:id="rId28"/>
-    <sheet name="LIC Housing Finance" sheetId="29" r:id="rId29"/>
+    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
+    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -1950,242 +1949,6 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.9</v>
-      </c>
-      <c r="C2">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 99 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.8</v>
-      </c>
-      <c r="C5">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>5.9</v>
-      </c>
-      <c r="C7">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
-      </c>
-      <c r="B9">
-        <v>5.85</v>
-      </c>
-      <c r="C9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>372 days</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.05</v>
-      </c>
-      <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2343,7 +2106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -2542,6 +2305,198 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2762,7 +2717,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2782,43 +2737,43 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -2826,128 +2781,95 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2974,24 +2896,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -2999,109 +2921,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3112,6 +3034,413 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3133,7 +3462,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -3144,535 +3473,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3699,134 +3621,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3838,7 +3760,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3858,139 +3780,62 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
         <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4017,57 +3862,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>1 year</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>2 years</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>3 years</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>4 years</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>5 years</v>
       </c>
       <c r="B6">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="C6">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4078,88 +3923,6 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -11,14 +11,14 @@
     <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
     <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
     <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="SBI" sheetId="9" r:id="rId9"/>
-    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="ICICI Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Axis Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="PNB" sheetId="12" r:id="rId12"/>
+    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="South Indian Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
     <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
     <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
@@ -583,7 +583,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -603,106 +603,205 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 to 45 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 to 90 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 to 184 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
         <v>6.5</v>
       </c>
-      <c r="C10">
+      <c r="C16">
         <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -729,73 +828,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 - 14 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>15 - 30 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>31 - 45 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>46 - 90 Days</v>
       </c>
       <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
         <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>91 Days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>92 Days - 179 Days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>180 Days</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -806,18 +905,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>181 Days to 269 Days</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>270 Days</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -828,101 +927,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>271 Days to 363 Days</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>364 Days</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>365 Days to less than 15 Months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>15 Months - less than 18 Months</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>18 months - less than 2 years</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>2 years- less than 3 years</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>3 years and above but less than 4 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>4 years and above but less than 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>5 years and above upto and inclusive of 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -933,231 +1032,6 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1426,7 +1300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1629,7 +1503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1810,7 +1684,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1943,6 +1817,242 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4905,7 +5015,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -4925,51 +5035,51 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 45 days</v>
+        <v>7 to 45 Days</v>
       </c>
       <c r="B2">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 days to 179 days</v>
+        <v>46 to 90 Days</v>
       </c>
       <c r="B3">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>180 days to 210 days</v>
+        <v>91 to 184 Days</v>
       </c>
       <c r="B4">
-        <v>5.65</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>6.15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>211 days to less than 1 year</v>
+        <v>185 to &lt; 1 Year</v>
       </c>
       <c r="B5">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to less than 2 years</v>
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
         <v>6.25</v>
@@ -4980,62 +5090,51 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>5 years and up to 10 years</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>7.05</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 Year</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.8</v>
-      </c>
-      <c r="C11">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -11,26 +11,21 @@
     <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
     <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
     <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="ICICI Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Axis Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="PNB" sheetId="12" r:id="rId12"/>
-    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="South Indian Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="SBI" sheetId="9" r:id="rId9"/>
+    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="PNB" sheetId="13" r:id="rId13"/>
+    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
-    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
-    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
-    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
-    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="Bank of India" sheetId="18" r:id="rId18"/>
+    <sheet name="RBL Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="IDBI Bank" sheetId="20" r:id="rId20"/>
+    <sheet name="Bandhan Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="PNB Housing Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="LIC Housing Finance" sheetId="23" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
@@ -583,7 +578,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C10"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -603,205 +598,106 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>7 to 45 Days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>46 to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>91 to 184 Days</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>185 to &lt; 1 Year</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>1 Year to &lt; 18 Months</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>18 Months to 2 Years</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
         <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -828,73 +724,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 Days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 - 30 Days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 Days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 - 90 Days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 Days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 Days</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -905,18 +801,18 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>270 Days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
         <v>5.5</v>
@@ -927,101 +823,101 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>364 Days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -1032,6 +928,231 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1300,7 +1421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1503,7 +1624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1684,7 +1805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1817,242 +1938,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.9</v>
-      </c>
-      <c r="C2">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 99 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.8</v>
-      </c>
-      <c r="C5">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>5.9</v>
-      </c>
-      <c r="C7">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
-      </c>
-      <c r="B9">
-        <v>5.85</v>
-      </c>
-      <c r="C9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>372 days</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.05</v>
-      </c>
-      <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2218,209 +2103,6 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.45</v>
-      </c>
-      <c r="C16">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
-      </c>
-      <c r="B17">
-        <v>6.75</v>
-      </c>
-      <c r="C17">
-        <v>7.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2607,6 +2289,165 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2827,7 +2668,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2847,84 +2688,84 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>07-30 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>31-45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>46- 60 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.35</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>61- 90 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>91 days to 6 months</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>6 months 1 day to 270 Days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>271 days to &lt; 1 year</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>1 Year</v>
       </c>
       <c r="B9">
         <v>6.2</v>
@@ -2933,53 +2774,109 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>&gt; 2 Years to &lt;3years</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>3 years to &lt;5 years</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.35</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>5 years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3006,73 +2903,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -3083,7 +2980,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -3094,7 +2991,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -3105,35 +3002,35 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3144,731 +3041,6 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3950,9 +3122,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C2"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3972,155 +3144,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>3 months but less than 6 months</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B4">
-        <v>6.75</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
-      </c>
-      <c r="C5">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B6">
-        <v>6.85</v>
-      </c>
-      <c r="C6">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B7">
-        <v>6.9</v>
-      </c>
-      <c r="C7">
-        <v>7.15</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5015,7 +4050,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -5035,51 +4070,51 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 to 45 Days</v>
+        <v>7 days to 45 days</v>
       </c>
       <c r="B2">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="C2">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 to 90 Days</v>
+        <v>46 days to 179 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 to 184 Days</v>
+        <v>180 days to 210 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>5.65</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
+        <v>211 days to less than 1 year</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
+        <v>1 Year to less than 2 years</v>
       </c>
       <c r="B6">
         <v>6.25</v>
@@ -5090,51 +4125,62 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B7">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="C7">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B8">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="C8">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
+        <v>5 years and up to 10 years</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
+        <v>1 Year</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.8</v>
+      </c>
+      <c r="C11">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -20,12 +20,17 @@
     <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
     <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
     <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of India" sheetId="18" r:id="rId18"/>
-    <sheet name="RBL Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="IDBI Bank" sheetId="20" r:id="rId20"/>
-    <sheet name="Bandhan Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="PNB Housing Finance" sheetId="22" r:id="rId22"/>
-    <sheet name="LIC Housing Finance" sheetId="23" r:id="rId23"/>
+    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
+    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -2103,6 +2108,209 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.45</v>
+      </c>
+      <c r="C16">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
+      </c>
+      <c r="B17">
+        <v>6.75</v>
+      </c>
+      <c r="C17">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2289,165 +2497,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 240 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>241 days to 364 days</v>
-      </c>
-      <c r="B7">
-        <v>6.05</v>
-      </c>
-      <c r="C7">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>18 months to 24 months</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
-      </c>
-      <c r="B11">
-        <v>7.2</v>
-      </c>
-      <c r="C11">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B13">
-        <v>6.7</v>
-      </c>
-      <c r="C13">
-        <v>7.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2668,7 +2717,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2688,84 +2737,84 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>07-30 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31-45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46- 60 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.85</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>61- 90 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 6 months</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.35</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
         <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>6.3</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 Year</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
         <v>6.2</v>
@@ -2774,109 +2823,53 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.35</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.85</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2903,73 +2896,73 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -2980,7 +2973,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -2991,7 +2984,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -3002,35 +2995,35 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3041,6 +3034,731 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15-30 days</v>
+      </c>
+      <c r="B3">
+        <v>3.75</v>
+      </c>
+      <c r="C3">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.75</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 -59 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 - 90 days</v>
+      </c>
+      <c r="B6">
+        <v>4.5</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>91 -179 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 -270 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>271-364 days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 yr to less than 2 yrs</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 yr to less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 yr to less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years &amp; above up to 10 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3122,7 +3840,89 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -3,34 +3,31 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Shivalik Small Finance Bank" sheetId="1" r:id="rId1"/>
-    <sheet name="Suryoday Small Finance Bank" sheetId="2" r:id="rId2"/>
-    <sheet name="Utkarsh Small Finance Bank" sheetId="3" r:id="rId3"/>
-    <sheet name="Unity Small Finance Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="Bajaj Finance" sheetId="5" r:id="rId5"/>
-    <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
-    <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
-    <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="SBI" sheetId="9" r:id="rId9"/>
-    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
-    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
-    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
-    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
-    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="Utkarsh Small Finance Bank" sheetId="1" r:id="rId1"/>
+    <sheet name="Unity Small Finance Bank" sheetId="2" r:id="rId2"/>
+    <sheet name="Mahindra Finance" sheetId="3" r:id="rId3"/>
+    <sheet name="Shriram City Union Finance" sheetId="4" r:id="rId4"/>
+    <sheet name="HDFC Bank" sheetId="5" r:id="rId5"/>
+    <sheet name="SBI" sheetId="6" r:id="rId6"/>
+    <sheet name="ICICI Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="Axis Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="PNB" sheetId="10" r:id="rId10"/>
+    <sheet name="IndusInd Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Yes Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="IDFC First Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="Canara Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Bank of Baroda" sheetId="15" r:id="rId15"/>
+    <sheet name="Bank of India" sheetId="16" r:id="rId16"/>
+    <sheet name="Bank of Maharashtra" sheetId="17" r:id="rId17"/>
+    <sheet name="RBL Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="IDBI Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="Indian Bank" sheetId="20" r:id="rId20"/>
+    <sheet name="Central Bank of India" sheetId="21" r:id="rId21"/>
+    <sheet name="Bandhan Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="PNB Housing Finance" sheetId="23" r:id="rId23"/>
+    <sheet name="KTDFC" sheetId="24" r:id="rId24"/>
+    <sheet name="LIC Housing Finance" sheetId="25" r:id="rId25"/>
   </sheets>
 </workbook>
 </file>
@@ -424,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -444,720 +441,133 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 45 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 29 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 days to 90 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>181 days to 370 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>6 months to less than 9 months</v>
+        <v>371 days to 665 days</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>6.25</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>9 months to 12 months</v>
+        <v>666 days</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>8.1</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>12 months 1 day to 18 months</v>
+        <v>667 days to 2 years</v>
       </c>
       <c r="B8">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>18 months  to 23 months</v>
+        <v>2 years (730 days) to 3 years (1095 days)</v>
       </c>
       <c r="B9">
         <v>7.5</v>
       </c>
       <c r="C9">
-        <v>7.75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>23 months 1 day to 27 months</v>
+        <v>Above 3 years to less than 4 years</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="C10">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>27 months 1 day to 36 months</v>
+        <v>4 years (1461 days) to 5 years (1826 days)</v>
       </c>
       <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
         <v>7.5</v>
-      </c>
-      <c r="C11">
-        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above 5 years to 10 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>60 months 1 day to 120 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 – 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 – 29 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 – 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.25</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 – 60 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61 days - 87 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -1426,7 +836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1629,7 +1039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1810,7 +1220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1943,6 +1353,560 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 Days to 45 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 Days to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 Days to 179 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>180 Days to 269 Days</v>
+      </c>
+      <c r="B5">
+        <v>5.25</v>
+      </c>
+      <c r="C5">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>270 Days to less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+      </c>
+      <c r="B7">
+        <v>6.25</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>444 Days ##</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>555 Days ##</v>
+      </c>
+      <c r="B9">
+        <v>6.6</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years &amp; above to less than 3 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 Years &amp; above to less than 5 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 Years &amp; above to 10 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.45</v>
+      </c>
+      <c r="C16">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
+      </c>
+      <c r="B17">
+        <v>6.75</v>
+      </c>
+      <c r="C17">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1969,134 +1933,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>444 Days ##</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>555 Days ##</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -2108,7 +2072,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2142,10 +2106,10 @@
         <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -2153,10 +2117,10 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
         <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
       </c>
     </row>
     <row r="5">
@@ -2164,15 +2128,15 @@
         <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 210 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
         <v>5.5</v>
@@ -2183,133 +2147,551 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>211 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>6.25</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.45</v>
-      </c>
-      <c r="C16">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
-      </c>
-      <c r="B17">
-        <v>6.75</v>
-      </c>
-      <c r="C17">
-        <v>7.25</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C21"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.75</v>
+      </c>
+      <c r="C4">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 164 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>165 days to 6 months</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Above 6 months to 201 days</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>202 days to 364 days</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>7.5</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 year 1 day</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 1 year 1 day to 500 days</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>501 days</v>
+      </c>
+      <c r="B13">
+        <v>7.8</v>
+      </c>
+      <c r="C13">
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>502 days to 18 months</v>
+      </c>
+      <c r="B14">
+        <v>6.75</v>
+      </c>
+      <c r="C14">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 18 months to 700 days</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>701 days</v>
+      </c>
+      <c r="B16">
+        <v>6.75</v>
+      </c>
+      <c r="C16">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>702 days to 998 days</v>
+      </c>
+      <c r="B17">
+        <v>6.75</v>
+      </c>
+      <c r="C17">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>999 days to 34 months</v>
+      </c>
+      <c r="B18">
+        <v>6.75</v>
+      </c>
+      <c r="C18">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>34 months to 3 years</v>
+      </c>
+      <c r="B19">
+        <v>6.75</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Above 3 years to 5 years</v>
+      </c>
+      <c r="B20">
+        <v>6.75</v>
+      </c>
+      <c r="C20">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -2331,90 +2713,90 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 to 14 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 30 days</v>
+        <v>15 to 29 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days to 45 days</v>
+        <v>30 to 45 days</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 days to 90 days</v>
+        <v>46 to 90 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>91 days to 179 days</v>
+        <v>91 to 120 days</v>
       </c>
       <c r="B6">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="C6">
-        <v>4.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>180 days to 210 days</v>
+        <v>121 to 180 days</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>211 days to 269 days</v>
+        <v>181 days to less than 9 months</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
+        <v>9 months to less than 1 year</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="10">
@@ -2422,26 +2804,26 @@
         <v>1 year</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
       </c>
       <c r="B11">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="C11">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>450 days</v>
+        <v>444 days (Ind Secure Product)</v>
       </c>
       <c r="B12">
         <v>6.6</v>
@@ -2452,40 +2834,40 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
+        <v>555 days (Ind Green Product)</v>
       </c>
       <c r="B13">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C13">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
+        <v>2 years to less than 3 years</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
+        <v>3 years to less than 5 years</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="C15">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
+        <v>5 years</v>
       </c>
       <c r="B16">
         <v>6</v>
@@ -2497,379 +2879,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4.25</v>
-      </c>
-      <c r="C3">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>4.65</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>6 month 1 day</v>
-      </c>
-      <c r="B6">
-        <v>6.5</v>
-      </c>
-      <c r="C6">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Above 6 months 1 day to 9 months</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>5.65</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Above 9 months to less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>7.25</v>
-      </c>
-      <c r="C9">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to less than 18 months</v>
-      </c>
-      <c r="B10">
-        <v>7.25</v>
-      </c>
-      <c r="C10">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B11">
-        <v>7.8</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 18 months to 2 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 2 years to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>7.25</v>
-      </c>
-      <c r="C13">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>8.1</v>
-      </c>
-      <c r="C14">
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to 3 years</v>
-      </c>
-      <c r="B15">
-        <v>7.25</v>
-      </c>
-      <c r="C15">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Above 3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.75</v>
-      </c>
-      <c r="C16">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B17">
-        <v>8.25</v>
-      </c>
-      <c r="C17">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Above 5 years to 10 years</v>
-      </c>
-      <c r="B18">
-        <v>7.25</v>
-      </c>
-      <c r="C18">
-        <v>7.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2896,7 +2905,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -2907,123 +2916,123 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3034,413 +3043,6 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3462,134 +3064,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3599,166 +3201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3840,7 +3283,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3922,7 +3365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>
@@ -3962,461 +3405,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 45 days</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>4.5</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>181 days to 370 days</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>371 days to 665 days</v>
-      </c>
-      <c r="B6">
-        <v>7.25</v>
-      </c>
-      <c r="C6">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>666 days</v>
-      </c>
-      <c r="B7">
-        <v>8.1</v>
-      </c>
-      <c r="C7">
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>667 days to 2 years</v>
-      </c>
-      <c r="B8">
-        <v>7.25</v>
-      </c>
-      <c r="C8">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>2 years (730 days) to 3 years (1095 days)</v>
-      </c>
-      <c r="B9">
-        <v>7.5</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 3 years to less than 4 years</v>
-      </c>
-      <c r="B10">
-        <v>7.25</v>
-      </c>
-      <c r="C10">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>4 years (1461 days) to 5 years (1826 days)</v>
-      </c>
-      <c r="B11">
-        <v>7</v>
-      </c>
-      <c r="C11">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 5 years to 10 years</v>
-      </c>
-      <c r="B12">
-        <v>6.75</v>
-      </c>
-      <c r="C12">
-        <v>7.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.75</v>
-      </c>
-      <c r="C4">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 164 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>165 days to 6 months</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Above 6 months to 201 days</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>202 days to 364 days</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>7.5</v>
-      </c>
-      <c r="C10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 year 1 day</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 1 year 1 day to 500 days</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>501 days</v>
-      </c>
-      <c r="B13">
-        <v>7.8</v>
-      </c>
-      <c r="C13">
-        <v>8.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>502 days to 18 months</v>
-      </c>
-      <c r="B14">
-        <v>6.75</v>
-      </c>
-      <c r="C14">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 18 months to 700 days</v>
-      </c>
-      <c r="B15">
-        <v>6.75</v>
-      </c>
-      <c r="C15">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>701 days</v>
-      </c>
-      <c r="B16">
-        <v>6.75</v>
-      </c>
-      <c r="C16">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>702 days to 998 days</v>
-      </c>
-      <c r="B17">
-        <v>6.75</v>
-      </c>
-      <c r="C17">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>999 days to 34 months</v>
-      </c>
-      <c r="B18">
-        <v>6.75</v>
-      </c>
-      <c r="C18">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>34 months to 3 years</v>
-      </c>
-      <c r="B19">
-        <v>6.75</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Above 3 years to 5 years</v>
-      </c>
-      <c r="B20">
-        <v>6.75</v>
-      </c>
-      <c r="C20">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Above 5 years to 10 years</v>
-      </c>
-      <c r="B21">
-        <v>6</v>
-      </c>
-      <c r="C21">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months to 14 months</v>
-      </c>
-      <c r="B2">
-        <v>6.6</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 months to 23 months</v>
-      </c>
-      <c r="B3">
-        <v>6.75</v>
-      </c>
-      <c r="C3">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>24 months to 60 months</v>
-      </c>
-      <c r="B4">
-        <v>6.95</v>
-      </c>
-      <c r="C4">
-        <v>7.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C9"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -4530,7 +3518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -4612,7 +3600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
@@ -4848,7 +3836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -4983,4 +3971,580 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 45 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 to 184 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>185 to &lt; 1 Year</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to &lt; 18 Months</v>
+      </c>
+      <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>18 Months to 2 Years</v>
+      </c>
+      <c r="B7">
+        <v>6.3</v>
+      </c>
+      <c r="C7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2 Years 1 Day to 3 Years</v>
+      </c>
+      <c r="B8">
+        <v>6.45</v>
+      </c>
+      <c r="C8">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>3 Years 1 Day to 5 Years</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5 Years 1 Day to 10 Years</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 – 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 – 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 – 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.25</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 – 60 days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>61 days - 87 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>88 days – 3 months 24 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>3 months 25 days &lt; 4 months</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>4 months &lt; 6 months</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>6 months &lt; 9 months</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
+        <v>6.5</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -3,31 +3,34 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Utkarsh Small Finance Bank" sheetId="1" r:id="rId1"/>
-    <sheet name="Unity Small Finance Bank" sheetId="2" r:id="rId2"/>
-    <sheet name="Mahindra Finance" sheetId="3" r:id="rId3"/>
-    <sheet name="Shriram City Union Finance" sheetId="4" r:id="rId4"/>
-    <sheet name="HDFC Bank" sheetId="5" r:id="rId5"/>
-    <sheet name="SBI" sheetId="6" r:id="rId6"/>
-    <sheet name="ICICI Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="Axis Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="PNB" sheetId="10" r:id="rId10"/>
-    <sheet name="IndusInd Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Yes Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="IDFC First Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="Canara Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Bank of Baroda" sheetId="15" r:id="rId15"/>
-    <sheet name="Bank of India" sheetId="16" r:id="rId16"/>
-    <sheet name="Bank of Maharashtra" sheetId="17" r:id="rId17"/>
-    <sheet name="RBL Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="IDBI Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="Indian Bank" sheetId="20" r:id="rId20"/>
-    <sheet name="Central Bank of India" sheetId="21" r:id="rId21"/>
-    <sheet name="Bandhan Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="PNB Housing Finance" sheetId="23" r:id="rId23"/>
-    <sheet name="KTDFC" sheetId="24" r:id="rId24"/>
-    <sheet name="LIC Housing Finance" sheetId="25" r:id="rId25"/>
+    <sheet name="Shivalik Small Finance Bank" sheetId="1" r:id="rId1"/>
+    <sheet name="Suryoday Small Finance Bank" sheetId="2" r:id="rId2"/>
+    <sheet name="Utkarsh Small Finance Bank" sheetId="3" r:id="rId3"/>
+    <sheet name="Unity Small Finance Bank" sheetId="4" r:id="rId4"/>
+    <sheet name="Bajaj Finance" sheetId="5" r:id="rId5"/>
+    <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
+    <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
+    <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="SBI" sheetId="9" r:id="rId9"/>
+    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="PNB" sheetId="13" r:id="rId13"/>
+    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
+    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -421,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -441,133 +444,720 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 45 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 days to 90 days</v>
+        <v>15 days to 29 days</v>
       </c>
       <c r="B3">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 days to 180 days</v>
+        <v>30 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>181 days to 370 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>371 days to 665 days</v>
+        <v>6 months to less than 9 months</v>
       </c>
       <c r="B6">
-        <v>7.25</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>666 days</v>
+        <v>9 months to 12 months</v>
       </c>
       <c r="B7">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>8.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>667 days to 2 years</v>
+        <v>12 months 1 day to 18 months</v>
       </c>
       <c r="B8">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="C8">
-        <v>7.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2 years (730 days) to 3 years (1095 days)</v>
+        <v>18 months  to 23 months</v>
       </c>
       <c r="B9">
         <v>7.5</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 3 years to less than 4 years</v>
+        <v>23 months 1 day to 27 months</v>
       </c>
       <c r="B10">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>4 years (1461 days) to 5 years (1826 days)</v>
+        <v>27 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="C11">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above 5 years to 10 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.25</v>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months 1 day to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 45 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 to 184 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>185 to &lt; 1 Year</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to &lt; 18 Months</v>
+      </c>
+      <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>18 Months to 2 Years</v>
+      </c>
+      <c r="B7">
+        <v>6.3</v>
+      </c>
+      <c r="C7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2 Years 1 Day to 3 Years</v>
+      </c>
+      <c r="B8">
+        <v>6.45</v>
+      </c>
+      <c r="C8">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>3 Years 1 Day to 5 Years</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5 Years 1 Day to 10 Years</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 – 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 – 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 – 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.25</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 – 60 days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>61 days - 87 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>88 days – 3 months 24 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>3 months 25 days &lt; 4 months</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>4 months &lt; 6 months</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>6 months &lt; 9 months</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
+        <v>6.5</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
@@ -836,7 +1426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1039,7 +1629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1220,7 +1810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1353,560 +1943,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.25</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
-      </c>
-      <c r="B5">
-        <v>5.25</v>
-      </c>
-      <c r="C5">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
-      </c>
-      <c r="B7">
-        <v>6.25</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>444 Days ##</v>
-      </c>
-      <c r="B8">
-        <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>555 Days ##</v>
-      </c>
-      <c r="B9">
-        <v>6.6</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.45</v>
-      </c>
-      <c r="C16">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
-      </c>
-      <c r="B17">
-        <v>6.75</v>
-      </c>
-      <c r="C17">
-        <v>7.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 30 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 179 days</v>
-      </c>
-      <c r="B6">
-        <v>4.25</v>
-      </c>
-      <c r="C6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>180 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.3</v>
-      </c>
-      <c r="C11">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>450 days</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1933,134 +1969,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 Days to 45 Days*</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>46 Days to 90 Days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>91 Days to 179 Days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>180 Days to 269 Days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>270 Days to less than 1 Year</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>444 Days ##</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>555 Days ##</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>2 Years &amp; above to less than 3 Years</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>3 Years &amp; above to less than 5 Years</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>5 Years &amp; above to 10 Years</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -2071,6 +2107,615 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.45</v>
+      </c>
+      <c r="C16">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
+      </c>
+      <c r="B17">
+        <v>6.75</v>
+      </c>
+      <c r="C17">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4.25</v>
+      </c>
+      <c r="C3">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>6 month 1 day</v>
+      </c>
+      <c r="B6">
+        <v>6.5</v>
+      </c>
+      <c r="C6">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Above 6 months 1 day to 9 months</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Above 9 months to less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>7.25</v>
+      </c>
+      <c r="C9">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to less than 18 months</v>
+      </c>
+      <c r="B10">
+        <v>7.25</v>
+      </c>
+      <c r="C10">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B11">
+        <v>7.8</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 18 months to 2 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 2 years to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>7.25</v>
+      </c>
+      <c r="C13">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>8.1</v>
+      </c>
+      <c r="C14">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to 3 years</v>
+      </c>
+      <c r="B15">
+        <v>7.25</v>
+      </c>
+      <c r="C15">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Above 3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.75</v>
+      </c>
+      <c r="C16">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B17">
+        <v>8.25</v>
+      </c>
+      <c r="C17">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B18">
+        <v>7.25</v>
+      </c>
+      <c r="C18">
+        <v>7.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2092,24 +2737,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2117,768 +2762,114 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.75</v>
-      </c>
-      <c r="C4">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 164 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>165 days to 6 months</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Above 6 months to 201 days</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>202 days to 364 days</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>7.5</v>
-      </c>
-      <c r="C10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>1 year 1 day</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 1 year 1 day to 500 days</v>
-      </c>
-      <c r="B12">
-        <v>6.5</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>501 days</v>
-      </c>
-      <c r="B13">
-        <v>7.8</v>
-      </c>
-      <c r="C13">
-        <v>8.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>502 days to 18 months</v>
-      </c>
-      <c r="B14">
-        <v>6.75</v>
-      </c>
-      <c r="C14">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 18 months to 700 days</v>
-      </c>
-      <c r="B15">
-        <v>6.75</v>
-      </c>
-      <c r="C15">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>701 days</v>
-      </c>
-      <c r="B16">
-        <v>6.75</v>
-      </c>
-      <c r="C16">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>702 days to 998 days</v>
-      </c>
-      <c r="B17">
-        <v>6.75</v>
-      </c>
-      <c r="C17">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>999 days to 34 months</v>
-      </c>
-      <c r="B18">
-        <v>6.75</v>
-      </c>
-      <c r="C18">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>34 months to 3 years</v>
-      </c>
-      <c r="B19">
-        <v>6.75</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Above 3 years to 5 years</v>
-      </c>
-      <c r="B20">
-        <v>6.75</v>
-      </c>
-      <c r="C20">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Above 5 years to 10 years</v>
-      </c>
-      <c r="B21">
-        <v>6</v>
-      </c>
-      <c r="C21">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2905,7 +2896,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -2916,123 +2907,123 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -3043,6 +3034,413 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -3064,134 +3462,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3201,7 +3599,166 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3283,7 +3840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3365,7 +3922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>
@@ -3405,6 +3962,461 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C12"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 45 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>4.5</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>181 days to 370 days</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>371 days to 665 days</v>
+      </c>
+      <c r="B6">
+        <v>7.25</v>
+      </c>
+      <c r="C6">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>666 days</v>
+      </c>
+      <c r="B7">
+        <v>8.1</v>
+      </c>
+      <c r="C7">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>667 days to 2 years</v>
+      </c>
+      <c r="B8">
+        <v>7.25</v>
+      </c>
+      <c r="C8">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2 years (730 days) to 3 years (1095 days)</v>
+      </c>
+      <c r="B9">
+        <v>7.5</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 3 years to less than 4 years</v>
+      </c>
+      <c r="B10">
+        <v>7.25</v>
+      </c>
+      <c r="C10">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>4 years (1461 days) to 5 years (1826 days)</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B12">
+        <v>6.75</v>
+      </c>
+      <c r="C12">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C21"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.75</v>
+      </c>
+      <c r="C4">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 164 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>165 days to 6 months</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Above 6 months to 201 days</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>202 days to 364 days</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>7.5</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 year 1 day</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 1 year 1 day to 500 days</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>501 days</v>
+      </c>
+      <c r="B13">
+        <v>7.8</v>
+      </c>
+      <c r="C13">
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>502 days to 18 months</v>
+      </c>
+      <c r="B14">
+        <v>6.75</v>
+      </c>
+      <c r="C14">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 18 months to 700 days</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>701 days</v>
+      </c>
+      <c r="B16">
+        <v>6.75</v>
+      </c>
+      <c r="C16">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>702 days to 998 days</v>
+      </c>
+      <c r="B17">
+        <v>6.75</v>
+      </c>
+      <c r="C17">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>999 days to 34 months</v>
+      </c>
+      <c r="B18">
+        <v>6.75</v>
+      </c>
+      <c r="C18">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>34 months to 3 years</v>
+      </c>
+      <c r="B19">
+        <v>6.75</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Above 3 years to 5 years</v>
+      </c>
+      <c r="B20">
+        <v>6.75</v>
+      </c>
+      <c r="C20">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months to 14 months</v>
+      </c>
+      <c r="B2">
+        <v>6.6</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months to 23 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>24 months to 60 months</v>
+      </c>
+      <c r="B4">
+        <v>6.95</v>
+      </c>
+      <c r="C4">
+        <v>7.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C9"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3518,7 +4530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -3600,7 +4612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
@@ -3836,7 +4848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -3971,580 +4983,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 – 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 – 29 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 – 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.25</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 – 60 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61 days - 87 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -3,28 +3,34 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Mahindra Finance" sheetId="1" r:id="rId1"/>
-    <sheet name="HDFC Bank" sheetId="2" r:id="rId2"/>
-    <sheet name="SBI" sheetId="3" r:id="rId3"/>
-    <sheet name="ICICI Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="Axis Bank" sheetId="5" r:id="rId5"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="6" r:id="rId6"/>
-    <sheet name="PNB" sheetId="7" r:id="rId7"/>
-    <sheet name="IndusInd Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Yes Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="IDFC First Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Canara Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
-    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
-    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDBI Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
-    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
-    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
-    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="Shivalik Small Finance Bank" sheetId="1" r:id="rId1"/>
+    <sheet name="Suryoday Small Finance Bank" sheetId="2" r:id="rId2"/>
+    <sheet name="Utkarsh Small Finance Bank" sheetId="3" r:id="rId3"/>
+    <sheet name="Unity Small Finance Bank" sheetId="4" r:id="rId4"/>
+    <sheet name="Bajaj Finance" sheetId="5" r:id="rId5"/>
+    <sheet name="Mahindra Finance" sheetId="6" r:id="rId6"/>
+    <sheet name="Shriram City Union Finance" sheetId="7" r:id="rId7"/>
+    <sheet name="HDFC Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="SBI" sheetId="9" r:id="rId9"/>
+    <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="PNB" sheetId="13" r:id="rId13"/>
+    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
+    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -418,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -438,100 +444,1373 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>6.85</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>18 months</v>
+        <v>15 days to 29 days</v>
       </c>
       <c r="B3">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>6.85</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>24 months</v>
+        <v>30 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>6.85</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>30 months</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>6.85</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>7.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>36 months</v>
+        <v>6 months to less than 9 months</v>
       </c>
       <c r="B6">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>42 months</v>
+        <v>9 months to 12 months</v>
       </c>
       <c r="B7">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>48 months</v>
+        <v>12 months 1 day to 18 months</v>
       </c>
       <c r="B8">
-        <v>7.45</v>
+        <v>6.75</v>
       </c>
       <c r="C8">
-        <v>7.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>60 months</v>
+        <v>18 months  to 23 months</v>
       </c>
       <c r="B9">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="C9">
-        <v>7.8</v>
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>23 months 1 day to 27 months</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>27 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.5</v>
+      </c>
+      <c r="C11">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months 1 day to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C10"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 45 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 to 184 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>185 to &lt; 1 Year</v>
+      </c>
+      <c r="B5">
+        <v>5.5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1 Year to &lt; 18 Months</v>
+      </c>
+      <c r="B6">
+        <v>6.25</v>
+      </c>
+      <c r="C6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>18 Months to 2 Years</v>
+      </c>
+      <c r="B7">
+        <v>6.3</v>
+      </c>
+      <c r="C7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2 Years 1 Day to 3 Years</v>
+      </c>
+      <c r="B8">
+        <v>6.45</v>
+      </c>
+      <c r="C8">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>3 Years 1 Day to 5 Years</v>
+      </c>
+      <c r="B9">
+        <v>6.5</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>5 Years 1 Day to 10 Years</v>
+      </c>
+      <c r="B10">
+        <v>6.5</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 – 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 – 29 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 – 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3.25</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 – 60 days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>61 days - 87 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>88 days – 3 months 24 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>3 months 25 days &lt; 4 months</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>4 months &lt; 6 months</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>6 months &lt; 9 months</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>9 months &lt; 1 year</v>
+      </c>
+      <c r="B11">
+        <v>5.75</v>
+      </c>
+      <c r="C11">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 year – 1 year 10 days</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 year 11 days &lt; 13 months</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13 months &lt; 15 months</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15 months &lt; 18 months</v>
+      </c>
+      <c r="B15">
+        <v>6.45</v>
+      </c>
+      <c r="C15">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B16">
+        <v>6.5</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years to 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.5</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.8</v>
+      </c>
+      <c r="C16">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C23"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 45 Days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 to 90 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 to 154 Days</v>
+      </c>
+      <c r="B5">
+        <v>4.9</v>
+      </c>
+      <c r="C5">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>155 Days</v>
+      </c>
+      <c r="B6">
+        <v>5.55</v>
+      </c>
+      <c r="C6">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>156 Days to 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.9</v>
+      </c>
+      <c r="C7">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 to 270 Days</v>
+      </c>
+      <c r="B8">
+        <v>5.6</v>
+      </c>
+      <c r="C8">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>271 Days to 302 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.6</v>
+      </c>
+      <c r="C9">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>303 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.55</v>
+      </c>
+      <c r="C10">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>304 Days to &gt;1 Year</v>
+      </c>
+      <c r="B11">
+        <v>5.6</v>
+      </c>
+      <c r="C11">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>&gt;1 Year to 389 Days</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>390 Days</v>
+      </c>
+      <c r="B14">
+        <v>6.3</v>
+      </c>
+      <c r="C14">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>391 Days to 443 Days</v>
+      </c>
+      <c r="B15">
+        <v>6.3</v>
+      </c>
+      <c r="C15">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>444 Days</v>
+      </c>
+      <c r="B16">
+        <v>6.6</v>
+      </c>
+      <c r="C16">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>445 Days to 665 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.3</v>
+      </c>
+      <c r="C17">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>666 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>667 Days to 2 Years</v>
+      </c>
+      <c r="B19">
+        <v>6.3</v>
+      </c>
+      <c r="C19">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>&gt;3 Years to 1203 Days</v>
+      </c>
+      <c r="B20">
+        <v>6.35</v>
+      </c>
+      <c r="C20">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>1204 Days</v>
+      </c>
+      <c r="B21">
+        <v>6.3</v>
+      </c>
+      <c r="C21">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>1205 Days to 5 Years</v>
+      </c>
+      <c r="B22">
+        <v>6.35</v>
+      </c>
+      <c r="C22">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>&gt;5 Years to 10 Years</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>6.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 days to 179 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 days</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B9">
+        <v>5.75</v>
+      </c>
+      <c r="C9">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>270 days to 364 days</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 Year to below 1 Year 6 Month</v>
+      </c>
+      <c r="B12">
+        <v>6.75</v>
+      </c>
+      <c r="C12">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 Year 6 months to below 1 Year 7 months</v>
+      </c>
+      <c r="B13">
+        <v>6.9</v>
+      </c>
+      <c r="C13">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>1 Year 7 months to below 2 Years</v>
+      </c>
+      <c r="B14">
+        <v>6.9</v>
+      </c>
+      <c r="C14">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2 Years to 3 Years</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Above 3 Years up to below 61 Months</v>
+      </c>
+      <c r="B16">
+        <v>6.65</v>
+      </c>
+      <c r="C16">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>61 Months and above</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C15"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 120 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>121 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 271 days</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>272 days to less than 12 months</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B9">
+        <v>6.65</v>
+      </c>
+      <c r="C9">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>12 months 1 day to less than 18 months</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.75</v>
+      </c>
+      <c r="C11">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months 1 day to less than 24 months</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>24 months to less than 36 months</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>36 months to less than 60 months</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -668,7 +1947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -827,7 +2106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1030,7 +2309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1222,7 +2501,221 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4.25</v>
+      </c>
+      <c r="C3">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>6 month 1 day</v>
+      </c>
+      <c r="B6">
+        <v>6.5</v>
+      </c>
+      <c r="C6">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Above 6 months 1 day to 9 months</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Above 9 months to less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>7.25</v>
+      </c>
+      <c r="C9">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to less than 18 months</v>
+      </c>
+      <c r="B10">
+        <v>7.25</v>
+      </c>
+      <c r="C10">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B11">
+        <v>7.8</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 18 months to 2 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 2 years to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>7.25</v>
+      </c>
+      <c r="C13">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>8.1</v>
+      </c>
+      <c r="C14">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to 3 years</v>
+      </c>
+      <c r="B15">
+        <v>7.25</v>
+      </c>
+      <c r="C15">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Above 3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.75</v>
+      </c>
+      <c r="C16">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B17">
+        <v>8.25</v>
+      </c>
+      <c r="C17">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B18">
+        <v>7.25</v>
+      </c>
+      <c r="C18">
+        <v>7.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1381,7 +2874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1540,7 +3033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -1755,7 +3248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1947,7 +3440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2106,7 +3599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2265,7 +3758,861 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months - 23 months</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>24 months - 35 months</v>
+      </c>
+      <c r="B3">
+        <v>6.85</v>
+      </c>
+      <c r="C3">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>36 months - 47 months</v>
+      </c>
+      <c r="B4">
+        <v>7.1</v>
+      </c>
+      <c r="C4">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>48 months - 59 months</v>
+      </c>
+      <c r="B5">
+        <v>7.1</v>
+      </c>
+      <c r="C5">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 months</v>
+      </c>
+      <c r="B6">
+        <v>7.25</v>
+      </c>
+      <c r="C6">
+        <v>7.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>3 months but less than 6 months</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C12"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 45 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>4.5</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>181 days to 370 days</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>371 days to 665 days</v>
+      </c>
+      <c r="B6">
+        <v>7.25</v>
+      </c>
+      <c r="C6">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>666 days</v>
+      </c>
+      <c r="B7">
+        <v>8.1</v>
+      </c>
+      <c r="C7">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>667 days to 2 years</v>
+      </c>
+      <c r="B8">
+        <v>7.25</v>
+      </c>
+      <c r="C8">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2 years (730 days) to 3 years (1095 days)</v>
+      </c>
+      <c r="B9">
+        <v>7.5</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 3 years to less than 4 years</v>
+      </c>
+      <c r="B10">
+        <v>7.25</v>
+      </c>
+      <c r="C10">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>4 years (1461 days) to 5 years (1826 days)</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B12">
+        <v>6.75</v>
+      </c>
+      <c r="C12">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C21"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.75</v>
+      </c>
+      <c r="C4">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 164 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>165 days to 6 months</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Above 6 months to 201 days</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>202 days to 364 days</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>7.5</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1 year 1 day</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 1 year 1 day to 500 days</v>
+      </c>
+      <c r="B12">
+        <v>6.5</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>501 days</v>
+      </c>
+      <c r="B13">
+        <v>7.8</v>
+      </c>
+      <c r="C13">
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>502 days to 18 months</v>
+      </c>
+      <c r="B14">
+        <v>6.75</v>
+      </c>
+      <c r="C14">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 18 months to 700 days</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>701 days</v>
+      </c>
+      <c r="B16">
+        <v>6.75</v>
+      </c>
+      <c r="C16">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>702 days to 998 days</v>
+      </c>
+      <c r="B17">
+        <v>6.75</v>
+      </c>
+      <c r="C17">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>999 days to 34 months</v>
+      </c>
+      <c r="B18">
+        <v>6.75</v>
+      </c>
+      <c r="C18">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>34 months to 3 years</v>
+      </c>
+      <c r="B19">
+        <v>6.75</v>
+      </c>
+      <c r="C19">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Above 3 years to 5 years</v>
+      </c>
+      <c r="B20">
+        <v>6.75</v>
+      </c>
+      <c r="C20">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Above 5 years to 10 years</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months to 14 months</v>
+      </c>
+      <c r="B2">
+        <v>6.6</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months to 23 months</v>
+      </c>
+      <c r="B3">
+        <v>6.75</v>
+      </c>
+      <c r="C3">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>24 months to 60 months</v>
+      </c>
+      <c r="B4">
+        <v>6.95</v>
+      </c>
+      <c r="C4">
+        <v>7.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C9"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B2">
+        <v>6.6</v>
+      </c>
+      <c r="C2">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B3">
+        <v>6.6</v>
+      </c>
+      <c r="C3">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>24 months</v>
+      </c>
+      <c r="B4">
+        <v>6.85</v>
+      </c>
+      <c r="C4">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B5">
+        <v>6.85</v>
+      </c>
+      <c r="C5">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>36 months</v>
+      </c>
+      <c r="B6">
+        <v>7.4</v>
+      </c>
+      <c r="C6">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>42 months</v>
+      </c>
+      <c r="B7">
+        <v>7.4</v>
+      </c>
+      <c r="C7">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>48 months</v>
+      </c>
+      <c r="B8">
+        <v>7.45</v>
+      </c>
+      <c r="C8">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>60 months</v>
+      </c>
+      <c r="B9">
+        <v>7.45</v>
+      </c>
+      <c r="C9">
+        <v>7.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months</v>
+      </c>
+      <c r="B2">
+        <v>6.85</v>
+      </c>
+      <c r="C2">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 months (digital only)</v>
+      </c>
+      <c r="B3">
+        <v>7.1</v>
+      </c>
+      <c r="C3">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>18 months – 23 months</v>
+      </c>
+      <c r="B4">
+        <v>7.05</v>
+      </c>
+      <c r="C4">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>24 months – 35 months</v>
+      </c>
+      <c r="B5">
+        <v>7.1</v>
+      </c>
+      <c r="C5">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>36 months – 60 months</v>
+      </c>
+      <c r="B6">
+        <v>7.5</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C20"/>
   <cols>
@@ -2501,209 +4848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months - 23 months</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>24 months - 35 months</v>
-      </c>
-      <c r="B3">
-        <v>6.85</v>
-      </c>
-      <c r="C3">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>36 months - 47 months</v>
-      </c>
-      <c r="B4">
-        <v>7.1</v>
-      </c>
-      <c r="C4">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>48 months - 59 months</v>
-      </c>
-      <c r="B5">
-        <v>7.1</v>
-      </c>
-      <c r="C5">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 months</v>
-      </c>
-      <c r="B6">
-        <v>7.25</v>
-      </c>
-      <c r="C6">
-        <v>7.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>3 months but less than 6 months</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -2838,1233 +4983,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 45 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 to 184 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
-      </c>
-      <c r="B5">
-        <v>5.5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1 Year to &lt; 18 Months</v>
-      </c>
-      <c r="B6">
-        <v>6.25</v>
-      </c>
-      <c r="C6">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>18 Months to 2 Years</v>
-      </c>
-      <c r="B7">
-        <v>6.3</v>
-      </c>
-      <c r="C7">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2 Years 1 Day to 3 Years</v>
-      </c>
-      <c r="B8">
-        <v>6.45</v>
-      </c>
-      <c r="C8">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3 Years 1 Day to 5 Years</v>
-      </c>
-      <c r="B9">
-        <v>6.5</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5 Years 1 Day to 10 Years</v>
-      </c>
-      <c r="B10">
-        <v>6.5</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 – 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 – 29 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 – 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.25</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 – 60 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>61 days - 87 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
-      </c>
-      <c r="B11">
-        <v>5.75</v>
-      </c>
-      <c r="C11">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
-      </c>
-      <c r="B15">
-        <v>6.45</v>
-      </c>
-      <c r="C15">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B16">
-        <v>6.5</v>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years to 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.5</v>
-      </c>
-      <c r="C19">
-        <v>7.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C23"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 45 Days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 to 90 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 to 154 Days</v>
-      </c>
-      <c r="B5">
-        <v>4.9</v>
-      </c>
-      <c r="C5">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>155 Days</v>
-      </c>
-      <c r="B6">
-        <v>5.55</v>
-      </c>
-      <c r="C6">
-        <v>6.05</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>156 Days to 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.9</v>
-      </c>
-      <c r="C7">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 to 270 Days</v>
-      </c>
-      <c r="B8">
-        <v>5.6</v>
-      </c>
-      <c r="C8">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271 Days to 302 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.6</v>
-      </c>
-      <c r="C9">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>303 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.55</v>
-      </c>
-      <c r="C10">
-        <v>6.05</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>304 Days to &gt;1 Year</v>
-      </c>
-      <c r="B11">
-        <v>5.6</v>
-      </c>
-      <c r="C11">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>&gt;1 Year to 389 Days</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>390 Days</v>
-      </c>
-      <c r="B14">
-        <v>6.3</v>
-      </c>
-      <c r="C14">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>391 Days to 443 Days</v>
-      </c>
-      <c r="B15">
-        <v>6.3</v>
-      </c>
-      <c r="C15">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>444 Days</v>
-      </c>
-      <c r="B16">
-        <v>6.6</v>
-      </c>
-      <c r="C16">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>445 Days to 665 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.3</v>
-      </c>
-      <c r="C17">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>666 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>667 Days to 2 Years</v>
-      </c>
-      <c r="B19">
-        <v>6.3</v>
-      </c>
-      <c r="C19">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>&gt;3 Years to 1203 Days</v>
-      </c>
-      <c r="B20">
-        <v>6.35</v>
-      </c>
-      <c r="C20">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>1204 Days</v>
-      </c>
-      <c r="B21">
-        <v>6.3</v>
-      </c>
-      <c r="C21">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>1205 Days to 5 Years</v>
-      </c>
-      <c r="B22">
-        <v>6.35</v>
-      </c>
-      <c r="C22">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>&gt;5 Years to 10 Years</v>
-      </c>
-      <c r="B23">
-        <v>6</v>
-      </c>
-      <c r="C23">
-        <v>6.8</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C23"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 days to 179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 days</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B9">
-        <v>5.75</v>
-      </c>
-      <c r="C9">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>270 days to 364 days</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
-      </c>
-      <c r="B12">
-        <v>6.75</v>
-      </c>
-      <c r="C12">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
-      </c>
-      <c r="B13">
-        <v>6.9</v>
-      </c>
-      <c r="C13">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.9</v>
-      </c>
-      <c r="C14">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>2 Years to 3 Years</v>
-      </c>
-      <c r="B15">
-        <v>7</v>
-      </c>
-      <c r="C15">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
-      </c>
-      <c r="B16">
-        <v>6.65</v>
-      </c>
-      <c r="C16">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>61 Months and above</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 120 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>121 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 271 days</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>272 days to less than 12 months</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>12 months</v>
-      </c>
-      <c r="B9">
-        <v>6.65</v>
-      </c>
-      <c r="C9">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>12 months 1 day to less than 18 months</v>
-      </c>
-      <c r="B10">
-        <v>6.75</v>
-      </c>
-      <c r="C10">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.75</v>
-      </c>
-      <c r="C11">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months 1 day to less than 24 months</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>24 months to less than 36 months</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>36 months to less than 60 months</v>
-      </c>
-      <c r="B14">
-        <v>7</v>
-      </c>
-      <c r="C14">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B15">
-        <v>6.75</v>
-      </c>
-      <c r="C15">
-        <v>7.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -14,23 +14,22 @@
     <sheet name="SBI" sheetId="9" r:id="rId9"/>
     <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
     <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
-    <sheet name="PNB" sheetId="13" r:id="rId13"/>
-    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
-    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
-    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
-    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
-    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
-    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
-    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
-    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
+    <sheet name="PNB" sheetId="12" r:id="rId12"/>
+    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Canara Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Bank of Baroda" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of India" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of Maharashtra" sheetId="19" r:id="rId19"/>
+    <sheet name="RBL Bank" sheetId="20" r:id="rId20"/>
+    <sheet name="IDBI Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="Indian Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Central Bank of India" sheetId="23" r:id="rId23"/>
+    <sheet name="Bandhan Bank" sheetId="24" r:id="rId24"/>
+    <sheet name="PNB Housing Finance" sheetId="25" r:id="rId25"/>
+    <sheet name="KTDFC" sheetId="26" r:id="rId26"/>
+    <sheet name="LIC Housing Finance" sheetId="27" r:id="rId27"/>
   </sheets>
 </workbook>
 </file>
@@ -934,231 +933,6 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.8</v>
-      </c>
-      <c r="C16">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -1426,7 +1200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1629,7 +1403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1810,7 +1584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1947,7 +1721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2106,7 +1880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -2309,7 +2083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -2497,6 +2271,165 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.6</v>
+      </c>
+      <c r="C2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>3.75</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 119 days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>120 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to 364 days</v>
+      </c>
+      <c r="B8">
+        <v>5.25</v>
+      </c>
+      <c r="C8">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 2 years</v>
+      </c>
+      <c r="B10">
+        <v>6.15</v>
+      </c>
+      <c r="C10">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 2 years to 3 years</v>
+      </c>
+      <c r="B11">
+        <v>5.25</v>
+      </c>
+      <c r="C11">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above3 years to 5 years</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 5 years</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>5.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2737,24 +2670,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -2762,109 +2695,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -2875,6 +2808,413 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2896,7 +3236,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -2907,535 +3247,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3462,134 +3395,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -3601,7 +3534,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3621,139 +3554,62 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
         <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3780,57 +3636,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>1 year</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>2 years</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>3 years</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>4 years</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>5 years</v>
       </c>
       <c r="B6">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="C6">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3841,88 +3697,6 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -14,22 +14,23 @@
     <sheet name="SBI" sheetId="9" r:id="rId9"/>
     <sheet name="ICICI Bank" sheetId="10" r:id="rId10"/>
     <sheet name="Axis Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="PNB" sheetId="12" r:id="rId12"/>
-    <sheet name="IndusInd Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="Yes Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDFC First Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Canara Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Bank of Baroda" sheetId="17" r:id="rId17"/>
-    <sheet name="Bank of India" sheetId="18" r:id="rId18"/>
-    <sheet name="Bank of Maharashtra" sheetId="19" r:id="rId19"/>
-    <sheet name="RBL Bank" sheetId="20" r:id="rId20"/>
-    <sheet name="IDBI Bank" sheetId="21" r:id="rId21"/>
-    <sheet name="Indian Bank" sheetId="22" r:id="rId22"/>
-    <sheet name="Central Bank of India" sheetId="23" r:id="rId23"/>
-    <sheet name="Bandhan Bank" sheetId="24" r:id="rId24"/>
-    <sheet name="PNB Housing Finance" sheetId="25" r:id="rId25"/>
-    <sheet name="KTDFC" sheetId="26" r:id="rId26"/>
-    <sheet name="LIC Housing Finance" sheetId="27" r:id="rId27"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="12" r:id="rId12"/>
+    <sheet name="PNB" sheetId="13" r:id="rId13"/>
+    <sheet name="IndusInd Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Yes Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDFC First Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Canara Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Bank of Baroda" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank of India" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="20" r:id="rId20"/>
+    <sheet name="RBL Bank" sheetId="21" r:id="rId21"/>
+    <sheet name="IDBI Bank" sheetId="22" r:id="rId22"/>
+    <sheet name="Indian Bank" sheetId="23" r:id="rId23"/>
+    <sheet name="Central Bank of India" sheetId="24" r:id="rId24"/>
+    <sheet name="Bandhan Bank" sheetId="25" r:id="rId25"/>
+    <sheet name="PNB Housing Finance" sheetId="26" r:id="rId26"/>
+    <sheet name="KTDFC" sheetId="27" r:id="rId27"/>
+    <sheet name="LIC Housing Finance" sheetId="28" r:id="rId28"/>
   </sheets>
 </workbook>
 </file>
@@ -933,6 +934,231 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.65</v>
+      </c>
+      <c r="C16">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -1200,7 +1426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1403,7 +1629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -1584,7 +1810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -1721,7 +1947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1880,7 +2106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -2083,7 +2309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -2271,165 +2497,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2670,24 +2737,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2695,109 +2762,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -2808,6 +2875,165 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -3022,7 +3248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -3210,165 +3436,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3395,134 +3462,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -3534,7 +3601,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3554,62 +3621,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
         <v>7.25</v>
       </c>
-      <c r="C6">
-        <v>7.5</v>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3636,57 +3780,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2 years</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3 years</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4 years</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5 years</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -3697,6 +3841,88 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -2715,7 +2715,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C25"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2735,205 +2735,271 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>45 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B4">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>61 days - 87 days</v>
+        <v>10 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>11 days &lt; 13 months</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B11">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>14 days</v>
       </c>
       <c r="B14">
-        <v>6.25</v>
+        <v>2.75</v>
       </c>
       <c r="C14">
-        <v>6.75</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>29 days</v>
       </c>
       <c r="B15">
-        <v>6.45</v>
+        <v>2.75</v>
       </c>
       <c r="C15">
-        <v>6.95</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>24 days</v>
       </c>
       <c r="B16">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>25 days &lt; 4 months</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>3.75</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>5 years to 10 years</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>18 Months &lt; 2 years</v>
+      </c>
+      <c r="B20">
+        <v>6.3</v>
+      </c>
+      <c r="C20">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2 years &lt; 3 years</v>
+      </c>
+      <c r="B21">
+        <v>6.2</v>
+      </c>
+      <c r="C21">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>3 years &lt; 5 years</v>
+      </c>
+      <c r="B22">
+        <v>6.2</v>
+      </c>
+      <c r="C22">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>60 days</v>
+      </c>
+      <c r="B23">
+        <v>4.5</v>
+      </c>
+      <c r="C23">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>24 days</v>
+      </c>
+      <c r="B24">
+        <v>5.45</v>
+      </c>
+      <c r="C24">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>4 months &lt; 6 months</v>
+      </c>
+      <c r="B25">
+        <v>5.45</v>
+      </c>
+      <c r="C25">
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C25"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -2715,7 +2715,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C19"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2735,271 +2735,205 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>45 days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>61 days - 87 days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="C4">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>9 months &lt; 1 year</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>10 days</v>
+        <v>61 days - 87 days</v>
       </c>
       <c r="B6">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>11 days &lt; 13 months</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>13 months &lt; 15 months</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>15 months &lt; 18 months</v>
+        <v>4 months &lt; 6 months</v>
       </c>
       <c r="B9">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>6.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 Months &lt; 2 years</v>
+        <v>6 months &lt; 9 months</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="C10">
-        <v>6.15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years &lt; 3 years</v>
+        <v>9 months &lt; 1 year</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="C11">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years &lt; 5 years</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>6.15</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to 10 years</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>14 days</v>
+        <v>13 months &lt; 15 months</v>
       </c>
       <c r="B14">
-        <v>2.75</v>
+        <v>6.25</v>
       </c>
       <c r="C14">
-        <v>2.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>29 days</v>
+        <v>15 months &lt; 18 months</v>
       </c>
       <c r="B15">
-        <v>2.75</v>
+        <v>6.45</v>
       </c>
       <c r="C15">
-        <v>2.75</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>24 days</v>
+        <v>18 Months &lt; 2 years</v>
       </c>
       <c r="B16">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="C16">
-        <v>4.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>25 days &lt; 4 months</v>
+        <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="C17">
-        <v>3.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4 months &lt; 6 months</v>
+        <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="C18">
-        <v>4.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>6 months &lt; 9 months</v>
+        <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="C19">
-        <v>6.05</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>18 Months &lt; 2 years</v>
-      </c>
-      <c r="B20">
-        <v>6.3</v>
-      </c>
-      <c r="C20">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>2 years &lt; 3 years</v>
-      </c>
-      <c r="B21">
-        <v>6.2</v>
-      </c>
-      <c r="C21">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>3 years &lt; 5 years</v>
-      </c>
-      <c r="B22">
-        <v>6.2</v>
-      </c>
-      <c r="C22">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>60 days</v>
-      </c>
-      <c r="B23">
-        <v>4.5</v>
-      </c>
-      <c r="C23">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>24 days</v>
-      </c>
-      <c r="B24">
-        <v>5.45</v>
-      </c>
-      <c r="C24">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>4 months &lt; 6 months</v>
-      </c>
-      <c r="B25">
-        <v>5.45</v>
-      </c>
-      <c r="C25">
-        <v>5.5</v>
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -9,21 +9,20 @@
     <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
     <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
     <sheet name="PNB" sheetId="6" r:id="rId6"/>
-    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
-    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
-    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
-    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
-    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
+    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="Canara Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Bank of Baroda" sheetId="10" r:id="rId10"/>
+    <sheet name="Bank of India" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of Maharashtra" sheetId="12" r:id="rId12"/>
+    <sheet name="RBL Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="IDBI Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Indian Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
+    <sheet name="Bandhan Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="PNB Housing Finance" sheetId="18" r:id="rId18"/>
+    <sheet name="KTDFC" sheetId="19" r:id="rId19"/>
+    <sheet name="LIC Housing Finance" sheetId="20" r:id="rId20"/>
   </sheets>
 </workbook>
 </file>
@@ -653,165 +652,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.25</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
-      </c>
-      <c r="B5">
-        <v>5.25</v>
-      </c>
-      <c r="C5">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
-      </c>
-      <c r="B7">
-        <v>6.25</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>444 Days ##</v>
-      </c>
-      <c r="B8">
-        <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>555 Days ##</v>
-      </c>
-      <c r="B9">
-        <v>6.6</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -1013,7 +853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1201,6 +1041,165 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.6</v>
+      </c>
+      <c r="C2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>3.75</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 119 days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>120 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to 364 days</v>
+      </c>
+      <c r="B8">
+        <v>5.25</v>
+      </c>
+      <c r="C8">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 2 years</v>
+      </c>
+      <c r="B10">
+        <v>6.15</v>
+      </c>
+      <c r="C10">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 2 years to 3 years</v>
+      </c>
+      <c r="B11">
+        <v>5.25</v>
+      </c>
+      <c r="C11">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above3 years to 5 years</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 5 years</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>5.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1227,24 +1226,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -1252,109 +1251,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1365,6 +1364,413 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1386,7 +1792,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1397,535 +1803,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1952,134 +1951,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2091,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2111,139 +2110,62 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
         <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2270,57 +2192,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>1 year</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>2 years</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>3 years</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>4 years</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>5 years</v>
       </c>
       <c r="B6">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="C6">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2469,88 +2391,6 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3434,209 +3274,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>3.25</v>
-      </c>
-      <c r="C2">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 days to 179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 days</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B9">
-        <v>5.75</v>
-      </c>
-      <c r="C9">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>270 days to 364 days</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>1 Year to below 1 Year 6 Month</v>
-      </c>
-      <c r="B12">
-        <v>6.75</v>
-      </c>
-      <c r="C12">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>1 Year 6 months to below 1 Year 7 months</v>
-      </c>
-      <c r="B13">
-        <v>6.9</v>
-      </c>
-      <c r="C13">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>1 Year 7 months to below 2 Years</v>
-      </c>
-      <c r="B14">
-        <v>6.9</v>
-      </c>
-      <c r="C14">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>2 Years to 3 Years</v>
-      </c>
-      <c r="B15">
-        <v>7</v>
-      </c>
-      <c r="C15">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Above 3 Years up to below 61 Months</v>
-      </c>
-      <c r="B16">
-        <v>6.65</v>
-      </c>
-      <c r="C16">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>61 Months and above</v>
-      </c>
-      <c r="B17">
-        <v>6.5</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3816,7 +3453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -3951,4 +3588,163 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 Days to 45 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 Days to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 Days to 179 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>180 Days to 269 Days</v>
+      </c>
+      <c r="B5">
+        <v>5.25</v>
+      </c>
+      <c r="C5">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>270 Days to less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+      </c>
+      <c r="B7">
+        <v>6.25</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>444 Days ##</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>555 Days ##</v>
+      </c>
+      <c r="B9">
+        <v>6.6</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years &amp; above to less than 3 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 Years &amp; above to less than 5 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 Years &amp; above to 10 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -9,20 +9,21 @@
     <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
     <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
     <sheet name="PNB" sheetId="6" r:id="rId6"/>
-    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Canara Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Bank of Baroda" sheetId="10" r:id="rId10"/>
-    <sheet name="Bank of India" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of Maharashtra" sheetId="12" r:id="rId12"/>
-    <sheet name="RBL Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="IDBI Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Indian Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
-    <sheet name="Bandhan Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="PNB Housing Finance" sheetId="18" r:id="rId18"/>
-    <sheet name="KTDFC" sheetId="19" r:id="rId19"/>
-    <sheet name="LIC Housing Finance" sheetId="20" r:id="rId20"/>
+    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
+    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
+    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
+    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -652,6 +653,165 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 Days to 45 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 Days to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 Days to 179 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>180 Days to 269 Days</v>
+      </c>
+      <c r="B5">
+        <v>5.25</v>
+      </c>
+      <c r="C5">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>270 Days to less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+      </c>
+      <c r="B7">
+        <v>6.25</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>444 Days ##</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>555 Days ##</v>
+      </c>
+      <c r="B9">
+        <v>6.6</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years &amp; above to less than 3 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 Years &amp; above to less than 5 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 Years &amp; above to 10 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -853,7 +1013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1041,165 +1201,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1226,24 +1227,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -1251,109 +1252,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -1364,6 +1365,165 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -1578,7 +1738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1766,165 +1926,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1951,134 +1952,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2091,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2110,62 +2111,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
         <v>7.25</v>
       </c>
-      <c r="C6">
-        <v>7.5</v>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2192,57 +2270,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2 years</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3 years</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4 years</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5 years</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -2391,6 +2469,88 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3274,6 +3434,209 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>3.25</v>
+      </c>
+      <c r="C2">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 days to 179 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 days</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B9">
+        <v>5.75</v>
+      </c>
+      <c r="C9">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>270 days to 364 days</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1 Year to below 1 Year 6 Month</v>
+      </c>
+      <c r="B12">
+        <v>6.75</v>
+      </c>
+      <c r="C12">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1 Year 6 months to below 1 Year 7 months</v>
+      </c>
+      <c r="B13">
+        <v>6.9</v>
+      </c>
+      <c r="C13">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>1 Year 7 months to below 2 Years</v>
+      </c>
+      <c r="B14">
+        <v>6.9</v>
+      </c>
+      <c r="C14">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2 Years to 3 Years</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Above 3 Years up to below 61 Months</v>
+      </c>
+      <c r="B16">
+        <v>6.65</v>
+      </c>
+      <c r="C16">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>61 Months and above</v>
+      </c>
+      <c r="B17">
+        <v>6.5</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3453,7 +3816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -3588,163 +3951,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.25</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
-      </c>
-      <c r="B5">
-        <v>5.25</v>
-      </c>
-      <c r="C5">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
-      </c>
-      <c r="B7">
-        <v>6.25</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>444 Days ##</v>
-      </c>
-      <c r="B8">
-        <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>555 Days ##</v>
-      </c>
-      <c r="B9">
-        <v>6.6</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -12,18 +12,19 @@
     <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
     <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
     <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
-    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
-    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
-    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
-    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
+    <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Canara Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
+    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
+    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDBI Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
+    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
+    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
+    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
   </sheets>
 </workbook>
 </file>
@@ -653,6 +654,242 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -810,7 +1047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1013,7 +1250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1201,165 +1438,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1386,24 +1464,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -1411,109 +1489,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -1524,6 +1602,165 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -1738,7 +1975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1926,165 +2163,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2111,134 +2189,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -2250,7 +2328,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2270,62 +2348,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
         <v>7.25</v>
       </c>
-      <c r="C6">
-        <v>7.5</v>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2489,57 +2644,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2 years</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3 years</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4 years</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5 years</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -2550,6 +2705,88 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -17,14 +17,8 @@
     <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
     <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
     <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
-    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDBI Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
-    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
-    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
-    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
@@ -1603,165 +1597,6 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.75</v>
-      </c>
-      <c r="C5">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 240 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>241 days to 364 days</v>
-      </c>
-      <c r="B7">
-        <v>6.05</v>
-      </c>
-      <c r="C7">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>18 months to 24 months</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
-      </c>
-      <c r="B11">
-        <v>7.2</v>
-      </c>
-      <c r="C11">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>60 months to 120 months</v>
-      </c>
-      <c r="B13">
-        <v>6.7</v>
-      </c>
-      <c r="C13">
-        <v>7.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -1975,199 +1810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -2317,165 +1960,6 @@
       </c>
       <c r="C13">
         <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2622,208 +2106,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12 months - 23 months</v>
-      </c>
-      <c r="B2">
-        <v>6.7</v>
-      </c>
-      <c r="C2">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>24 months - 35 months</v>
-      </c>
-      <c r="B3">
-        <v>6.85</v>
-      </c>
-      <c r="C3">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>36 months - 47 months</v>
-      </c>
-      <c r="B4">
-        <v>7.1</v>
-      </c>
-      <c r="C4">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>48 months - 59 months</v>
-      </c>
-      <c r="B5">
-        <v>7.1</v>
-      </c>
-      <c r="C5">
-        <v>7.35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 months</v>
-      </c>
-      <c r="B6">
-        <v>7.25</v>
-      </c>
-      <c r="C6">
-        <v>7.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>3 months but less than 6 months</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C10"/>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -12,13 +12,18 @@
     <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
     <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
     <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Canara Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
-    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
+    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
+    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
     <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
+    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
+    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -648,7 +653,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -668,21 +673,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 Days to 45 Days*</v>
       </c>
       <c r="B2">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 90 days</v>
+        <v>46 Days to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -690,29 +695,29 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 days to 99 days</v>
+        <v>91 Days to 179 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
+        <v>180 Days to 269 Days</v>
       </c>
       <c r="B5">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="C5">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 270 days</v>
+        <v>270 Days to less than 1 Year</v>
       </c>
       <c r="B6">
         <v>5.5</v>
@@ -723,166 +728,484 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
       </c>
       <c r="B7">
-        <v>5.9</v>
+        <v>6.25</v>
       </c>
       <c r="C7">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>444 Days ##</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
+        <v>555 Days ##</v>
       </c>
       <c r="B9">
-        <v>5.85</v>
+        <v>6.6</v>
       </c>
       <c r="C9">
-        <v>6.35</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>372 days</v>
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
+        <v>2 Years &amp; above to less than 3 Years</v>
       </c>
       <c r="B11">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="C11">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months</v>
+        <v>3 Years &amp; above to less than 5 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
+        <v>5 Years &amp; above to 10 Years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.45</v>
+      </c>
+      <c r="C16">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
+      </c>
+      <c r="B17">
+        <v>6.75</v>
+      </c>
+      <c r="C17">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -904,534 +1227,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>444 Days ##</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>555 Days ##</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.45</v>
-      </c>
-      <c r="C16">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
-      </c>
-      <c r="B17">
-        <v>6.75</v>
-      </c>
-      <c r="C17">
-        <v>7.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 30 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 179 days</v>
-      </c>
-      <c r="B6">
-        <v>4.25</v>
-      </c>
-      <c r="C6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>180 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.3</v>
-      </c>
-      <c r="C11">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>450 days</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1458,24 +1386,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -1483,109 +1411,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1812,6 +1740,198 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -1965,6 +2085,247 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12 months - 23 months</v>
+      </c>
+      <c r="B2">
+        <v>6.7</v>
+      </c>
+      <c r="C2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>24 months - 35 months</v>
+      </c>
+      <c r="B3">
+        <v>6.85</v>
+      </c>
+      <c r="C3">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>36 months - 47 months</v>
+      </c>
+      <c r="B4">
+        <v>7.1</v>
+      </c>
+      <c r="C4">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>48 months - 59 months</v>
+      </c>
+      <c r="B5">
+        <v>7.1</v>
+      </c>
+      <c r="C5">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>60 months</v>
+      </c>
+      <c r="B6">
+        <v>7.25</v>
+      </c>
+      <c r="C6">
+        <v>7.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2102,6 +2463,126 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>3 months but less than 6 months</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -15,15 +15,13 @@
     <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
     <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
     <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
-    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
-    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
-    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
-    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
+    <sheet name="RBL Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="IDBI Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Indian Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
+    <sheet name="Bandhan Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="KTDFC" sheetId="18" r:id="rId18"/>
+    <sheet name="LIC Housing Finance" sheetId="19" r:id="rId19"/>
   </sheets>
 </workbook>
 </file>
@@ -1227,24 +1225,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -1252,109 +1250,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1365,6 +1363,413 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1386,7 +1791,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1397,535 +1802,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1952,134 +1950,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2090,165 +2088,6 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.95</v>
-      </c>
-      <c r="C2">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days - 30 days</v>
-      </c>
-      <c r="B3">
-        <v>2.95</v>
-      </c>
-      <c r="C3">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
-      </c>
-      <c r="B4">
-        <v>3.45</v>
-      </c>
-      <c r="C4">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
-      </c>
-      <c r="B5">
-        <v>4.2</v>
-      </c>
-      <c r="C5">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
-      </c>
-      <c r="B6">
-        <v>4.2</v>
-      </c>
-      <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -2270,62 +2109,100 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>1 year</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>2 years</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>3 years</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>4 years</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>5 years</v>
       </c>
       <c r="B6">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="C6">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>3 months but less than 6 months</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2463,126 +2340,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>3 months but less than 6 months</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -15,13 +15,15 @@
     <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
     <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
     <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
-    <sheet name="RBL Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="IDBI Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Indian Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
-    <sheet name="Bandhan Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="KTDFC" sheetId="18" r:id="rId18"/>
-    <sheet name="LIC Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
+    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
+    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
+    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -1225,24 +1227,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -1250,109 +1252,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -1363,6 +1365,165 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -1577,7 +1738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1765,165 +1926,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1950,134 +1952,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -2088,6 +2090,165 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days - 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.95</v>
+      </c>
+      <c r="C2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days - 30 days</v>
+      </c>
+      <c r="B3">
+        <v>2.95</v>
+      </c>
+      <c r="C3">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days - less than 2 months</v>
+      </c>
+      <c r="B4">
+        <v>3.45</v>
+      </c>
+      <c r="C4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2 months - less than 3 months</v>
+      </c>
+      <c r="B5">
+        <v>4.2</v>
+      </c>
+      <c r="C5">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3 months - less than 6 months</v>
+      </c>
+      <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
+        <v>7.25</v>
+      </c>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
   <cols>
@@ -2109,100 +2270,62 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2 years</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3 years</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4 years</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5 years</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>3 months but less than 6 months</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2340,6 +2463,126 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>3 months but less than 6 months</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -2735,7 +2735,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 – 14 days</v>
+        <v>14 days</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 – 29 days</v>
+        <v>29 days</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>30 – 45 days</v>
+        <v>45 days</v>
       </c>
       <c r="B4">
         <v>3.25</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 – 60 days</v>
+        <v>60 days</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>88 days – 3 months 24 days</v>
+        <v>24 days</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -2801,7 +2801,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3 months 25 days &lt; 4 months</v>
+        <v>25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1 year – 1 year 10 days</v>
+        <v>10 days</v>
       </c>
       <c r="B12">
         <v>6.25</v>
@@ -2856,7 +2856,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1 year 11 days &lt; 13 months</v>
+        <v>11 days &lt; 13 months</v>
       </c>
       <c r="B13">
         <v>6.25</v>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -12,18 +12,19 @@
     <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
     <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
     <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
-    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
-    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
-    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
-    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
+    <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Canara Bank" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
+    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
+    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="IDBI Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
+    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
+    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
+    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
+    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
   </sheets>
 </workbook>
 </file>
@@ -653,6 +654,242 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -810,7 +1047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -1013,7 +1250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1201,165 +1438,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1386,24 +1464,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -1411,109 +1489,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -1524,6 +1602,165 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -1738,7 +1975,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1926,165 +2163,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2111,134 +2189,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -2250,7 +2328,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2270,62 +2348,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
         <v>7.25</v>
       </c>
-      <c r="C6">
-        <v>7.5</v>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2489,57 +2644,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2 years</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3 years</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4 years</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5 years</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -2550,6 +2705,88 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>
@@ -2642,7 +2879,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>185 to &lt; 1 Year</v>
+        <v>185 Days to &lt; 1 Year</v>
       </c>
       <c r="B5">
         <v>5.5</v>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -12,19 +12,18 @@
     <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
     <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
     <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="South Indian Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Canara Bank" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of Baroda" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of India" sheetId="13" r:id="rId13"/>
-    <sheet name="Bank of Maharashtra" sheetId="14" r:id="rId14"/>
-    <sheet name="RBL Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="IDBI Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Indian Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="Central Bank of India" sheetId="18" r:id="rId18"/>
-    <sheet name="Bandhan Bank" sheetId="19" r:id="rId19"/>
-    <sheet name="PNB Housing Finance" sheetId="20" r:id="rId20"/>
-    <sheet name="KTDFC" sheetId="21" r:id="rId21"/>
-    <sheet name="LIC Housing Finance" sheetId="22" r:id="rId22"/>
+    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
+    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
+    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
+    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -654,7 +653,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -674,21 +673,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 Days to 45 Days*</v>
       </c>
       <c r="B2">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 90 days</v>
+        <v>46 Days to 90 Days</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -696,29 +695,29 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 days to 99 days</v>
+        <v>91 Days to 179 Days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
+        <v>180 Days to 269 Days</v>
       </c>
       <c r="B5">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="C5">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 270 days</v>
+        <v>270 Days to less than 1 Year</v>
       </c>
       <c r="B6">
         <v>5.5</v>
@@ -729,166 +728,484 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
       </c>
       <c r="B7">
-        <v>5.9</v>
+        <v>6.25</v>
       </c>
       <c r="C7">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>444 Days ##</v>
       </c>
       <c r="B8">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C8">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
+        <v>555 Days ##</v>
       </c>
       <c r="B9">
-        <v>5.85</v>
+        <v>6.6</v>
       </c>
       <c r="C9">
-        <v>6.35</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>372 days</v>
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
+        <v>2 Years &amp; above to less than 3 Years</v>
       </c>
       <c r="B11">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="C11">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>18 months</v>
+        <v>3 Years &amp; above to less than 5 Years</v>
       </c>
       <c r="B12">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
+        <v>5 Years &amp; above to 10 Years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C17"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 210 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>211 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5.75</v>
+      </c>
+      <c r="C7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days &amp; above and less than 1 year</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.25</v>
+      </c>
+      <c r="C9">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 400 days</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 400 days and upto 2 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above 2 Years and upto 3 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 3 Years and upto 5 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Above 5 Years and upto 10 Years</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 10 years (MACAD only)</v>
+      </c>
+      <c r="B15">
+        <v>5.5</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bob Square Drive Deposit Scheme (444 Days)</v>
+      </c>
+      <c r="B16">
+        <v>6.45</v>
+      </c>
+      <c r="C16">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
+      </c>
+      <c r="B17">
+        <v>6.75</v>
+      </c>
+      <c r="C17">
+        <v>7.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 30 days</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.5</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 179 days</v>
+      </c>
+      <c r="B6">
+        <v>4.25</v>
+      </c>
+      <c r="C6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>180 days to 210 days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>211 days to 269 days</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>270 days to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (except 400 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.3</v>
+      </c>
+      <c r="C11">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>450 days</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B13">
+        <v>6.3</v>
+      </c>
+      <c r="C13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B14">
+        <v>6.25</v>
+      </c>
+      <c r="C14">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>5 years to less than 8 years</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>8 years and above to 10 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -910,534 +1227,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
+        <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>444 Days ##</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>555 Days ##</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 180 days</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 210 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>211 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5.75</v>
-      </c>
-      <c r="C7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days &amp; above and less than 1 year</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.25</v>
-      </c>
-      <c r="C9">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 400 days</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 400 days and upto 2 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above 2 Years and upto 3 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 3 Years and upto 5 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Above 5 Years and upto 10 Years</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 10 years (MACAD only)</v>
-      </c>
-      <c r="B15">
-        <v>5.5</v>
-      </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bob Square Drive Deposit Scheme (444 Days)</v>
-      </c>
-      <c r="B16">
-        <v>6.45</v>
-      </c>
-      <c r="C16">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>bob Golden Goal Deposit Scheme (555 Days)</v>
-      </c>
-      <c r="B17">
-        <v>6.75</v>
-      </c>
-      <c r="C17">
-        <v>7.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 days to 30 days</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 179 days</v>
-      </c>
-      <c r="B6">
-        <v>4.25</v>
-      </c>
-      <c r="C6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>180 days to 210 days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>211 days to 269 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>270 days to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (except 400 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.3</v>
-      </c>
-      <c r="C11">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>450 days</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B13">
-        <v>6.3</v>
-      </c>
-      <c r="C13">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B14">
-        <v>6.25</v>
-      </c>
-      <c r="C14">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>5 years to less than 8 years</v>
-      </c>
-      <c r="B15">
-        <v>6</v>
-      </c>
-      <c r="C15">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>8 years and above to 10 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1464,24 +1386,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -1489,109 +1411,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1602,6 +1524,413 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1623,7 +1952,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1634,535 +1963,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2189,134 +2111,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2328,7 +2250,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2348,139 +2270,62 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
         <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2644,57 +2489,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>1 year</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>2 years</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>3 years</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>4 years</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>5 years</v>
       </c>
       <c r="B6">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="C6">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2705,88 +2550,6 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -7,11 +7,11 @@
     <sheet name="SBI" sheetId="2" r:id="rId2"/>
     <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
     <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
-    <sheet name="PNB" sheetId="6" r:id="rId6"/>
-    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="PNB" sheetId="5" r:id="rId5"/>
+    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
+    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="South Indian Bank" sheetId="9" r:id="rId9"/>
     <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
     <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
     <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
@@ -2940,231 +2940,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.65</v>
-      </c>
-      <c r="C16">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3432,7 +3207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -3635,7 +3410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -3816,7 +3591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -3951,4 +3726,240 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C20"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.9</v>
+      </c>
+      <c r="C2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 90 days</v>
+      </c>
+      <c r="B3">
+        <v>3.5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 days to 99 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>100 daysto 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.8</v>
+      </c>
+      <c r="C5">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>271 days to less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>5.9</v>
+      </c>
+      <c r="C7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>6.25</v>
+      </c>
+      <c r="C8">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Above 1 year to 371 days</v>
+      </c>
+      <c r="B9">
+        <v>5.85</v>
+      </c>
+      <c r="C9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>372 days</v>
+      </c>
+      <c r="B10">
+        <v>6.4</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>373 days to less than 18 months</v>
+      </c>
+      <c r="B11">
+        <v>6.05</v>
+      </c>
+      <c r="C11">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>18 months</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 18 months to less than 30 months</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>30 months</v>
+      </c>
+      <c r="B14">
+        <v>6.8</v>
+      </c>
+      <c r="C14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Above 30 months to less than 3 years</v>
+      </c>
+      <c r="B15">
+        <v>5.85</v>
+      </c>
+      <c r="C15">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B16">
+        <v>6.2</v>
+      </c>
+      <c r="C16">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5 years to less than 66 months</v>
+      </c>
+      <c r="B17">
+        <v>5.7</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>66 months (Green deposit)</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Above 66 months to upto and including 10 years</v>
+      </c>
+      <c r="B19">
+        <v>5.7</v>
+      </c>
+      <c r="C19">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tax Gain ( 5 Years )</v>
+      </c>
+      <c r="B20">
+        <v>5.7</v>
+      </c>
+      <c r="C20">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -7,11 +7,11 @@
     <sheet name="SBI" sheetId="2" r:id="rId2"/>
     <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
     <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="PNB" sheetId="5" r:id="rId5"/>
-    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
-    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="South Indian Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
+    <sheet name="PNB" sheetId="6" r:id="rId6"/>
+    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
     <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
     <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
     <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
@@ -2940,6 +2940,231 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.65</v>
+      </c>
+      <c r="C16">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3207,7 +3432,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -3410,7 +3635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -3591,7 +3816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -3726,240 +3951,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.9</v>
-      </c>
-      <c r="C2">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 90 days</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 days to 99 days</v>
-      </c>
-      <c r="B4">
-        <v>4.5</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>100 daysto 180 days</v>
-      </c>
-      <c r="B5">
-        <v>4.8</v>
-      </c>
-      <c r="C5">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>271 days to less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>5.9</v>
-      </c>
-      <c r="C7">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>6.25</v>
-      </c>
-      <c r="C8">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Above 1 year to 371 days</v>
-      </c>
-      <c r="B9">
-        <v>5.85</v>
-      </c>
-      <c r="C9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>372 days</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>373 days to less than 18 months</v>
-      </c>
-      <c r="B11">
-        <v>6.05</v>
-      </c>
-      <c r="C11">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>18 months</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 18 months to less than 30 months</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>30 months</v>
-      </c>
-      <c r="B14">
-        <v>6.8</v>
-      </c>
-      <c r="C14">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Above 30 months to less than 3 years</v>
-      </c>
-      <c r="B15">
-        <v>5.85</v>
-      </c>
-      <c r="C15">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B16">
-        <v>6.2</v>
-      </c>
-      <c r="C16">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>5 years to less than 66 months</v>
-      </c>
-      <c r="B17">
-        <v>5.7</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>66 months (Green deposit)</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Above 66 months to upto and including 10 years</v>
-      </c>
-      <c r="B19">
-        <v>5.7</v>
-      </c>
-      <c r="C19">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Tax Gain ( 5 Years )</v>
-      </c>
-      <c r="B20">
-        <v>5.7</v>
-      </c>
-      <c r="C20">
-        <v>6.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -7,23 +7,22 @@
     <sheet name="SBI" sheetId="2" r:id="rId2"/>
     <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
     <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
-    <sheet name="PNB" sheetId="6" r:id="rId6"/>
-    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
-    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
-    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
-    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
-    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
-    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
-    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
-    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
-    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
+    <sheet name="PNB" sheetId="5" r:id="rId5"/>
+    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
+    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="Canara Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Bank of Baroda" sheetId="10" r:id="rId10"/>
+    <sheet name="Bank of India" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of Maharashtra" sheetId="12" r:id="rId12"/>
+    <sheet name="RBL Bank" sheetId="13" r:id="rId13"/>
+    <sheet name="IDBI Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="Indian Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
+    <sheet name="Bandhan Bank" sheetId="17" r:id="rId17"/>
+    <sheet name="PNB Housing Finance" sheetId="18" r:id="rId18"/>
+    <sheet name="KTDFC" sheetId="19" r:id="rId19"/>
+    <sheet name="LIC Housing Finance" sheetId="20" r:id="rId20"/>
   </sheets>
 </workbook>
 </file>
@@ -653,165 +652,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.25</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
-      </c>
-      <c r="B5">
-        <v>5.25</v>
-      </c>
-      <c r="C5">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
-      </c>
-      <c r="B7">
-        <v>6.25</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>444 Days ##</v>
-      </c>
-      <c r="B8">
-        <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>555 Days ##</v>
-      </c>
-      <c r="B9">
-        <v>6.6</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -1013,7 +853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1201,6 +1041,165 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 30 days</v>
+      </c>
+      <c r="B2">
+        <v>2.6</v>
+      </c>
+      <c r="C2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>3.75</v>
+      </c>
+      <c r="C4">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 119 days</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>120 days to 180 days</v>
+      </c>
+      <c r="B6">
+        <v>4.75</v>
+      </c>
+      <c r="C6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>181 days to 270 days</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to 364 days</v>
+      </c>
+      <c r="B8">
+        <v>5.25</v>
+      </c>
+      <c r="C8">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 year to 2 years</v>
+      </c>
+      <c r="B10">
+        <v>6.15</v>
+      </c>
+      <c r="C10">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 2 years to 3 years</v>
+      </c>
+      <c r="B11">
+        <v>5.25</v>
+      </c>
+      <c r="C11">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Above3 years to 5 years</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Above 5 years</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>5.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1227,24 +1226,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 30 days</v>
+        <v>7 days to 14 days</v>
       </c>
       <c r="B2">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>31 days to 45 days</v>
+        <v>15 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -1252,109 +1251,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="C4">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 119 days</v>
+        <v>91 days to 180 days</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>120 days to 180 days</v>
+        <v>181 days to 240 days</v>
       </c>
       <c r="B6">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>181 days to 270 days</v>
+        <v>241 days to 364 days</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>271 days to 364 days</v>
+        <v>365 days to (12 months) 500 days</v>
       </c>
       <c r="B8">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year</v>
+        <v>501 days to less than 18 months)</v>
       </c>
       <c r="B9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
+        <v>18 months to 24 months</v>
       </c>
       <c r="B10">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
+        <v>24 months 1 day to 36 months</v>
       </c>
       <c r="B11">
-        <v>5.25</v>
+        <v>7.2</v>
       </c>
       <c r="C11">
-        <v>5.75</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
+        <v>36 months 1 day to 60 months</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Above 5 years</v>
+        <v>60 months to 120 months</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="C13">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1365,6 +1364,413 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C18"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>07-30 days</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>31-45 days</v>
+      </c>
+      <c r="B3">
+        <v>3.15</v>
+      </c>
+      <c r="C3">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46- 60 days</v>
+      </c>
+      <c r="B4">
+        <v>4.35</v>
+      </c>
+      <c r="C4">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>61- 90 days</v>
+      </c>
+      <c r="B5">
+        <v>4.6</v>
+      </c>
+      <c r="C5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 days to 6 months</v>
+      </c>
+      <c r="B6">
+        <v>5.35</v>
+      </c>
+      <c r="C6">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months 1 day to 270 Days</v>
+      </c>
+      <c r="B7">
+        <v>5.5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>271 days to &lt; 1 year</v>
+      </c>
+      <c r="B8">
+        <v>5.8</v>
+      </c>
+      <c r="C8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 Year</v>
+      </c>
+      <c r="B9">
+        <v>6.2</v>
+      </c>
+      <c r="C9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">&gt;1 Year to 2 Years
+(except 555 days &amp; 700 Days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>&gt; 2 Years to &lt;3years</v>
+      </c>
+      <c r="B11">
+        <v>6.5</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years to &lt;5 years</v>
+      </c>
+      <c r="B12">
+        <v>6.35</v>
+      </c>
+      <c r="C12">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>&gt;5 years to 7 years</v>
+      </c>
+      <c r="B14">
+        <v>5.95</v>
+      </c>
+      <c r="C14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>&gt;7 years to 10 years</v>
+      </c>
+      <c r="B15">
+        <v>5.9</v>
+      </c>
+      <c r="C15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>&gt;10 years to 20 years$</v>
+      </c>
+      <c r="B16">
+        <v>4.8</v>
+      </c>
+      <c r="C16">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1111 Days</v>
+      </c>
+      <c r="B17">
+        <v>6.35</v>
+      </c>
+      <c r="C17">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>370 Days</v>
+      </c>
+      <c r="B18">
+        <v>6.1</v>
+      </c>
+      <c r="C18">
+        <v>6.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>2.8</v>
+      </c>
+      <c r="C2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 to 29 days</v>
+      </c>
+      <c r="B3">
+        <v>2.8</v>
+      </c>
+      <c r="C3">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>30 to 45 days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 to 90 days</v>
+      </c>
+      <c r="B5">
+        <v>3.25</v>
+      </c>
+      <c r="C5">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 to 120 days</v>
+      </c>
+      <c r="B6">
+        <v>3.5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>121 to 180 days</v>
+      </c>
+      <c r="B7">
+        <v>3.85</v>
+      </c>
+      <c r="C7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>181 days to less than 9 months</v>
+      </c>
+      <c r="B8">
+        <v>4.5</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>9 months to less than 1 year</v>
+      </c>
+      <c r="B9">
+        <v>4.75</v>
+      </c>
+      <c r="C9">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B10">
+        <v>6.1</v>
+      </c>
+      <c r="C10">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
+      </c>
+      <c r="B11">
+        <v>6.2</v>
+      </c>
+      <c r="C11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>444 days (Ind Secure Product)</v>
+      </c>
+      <c r="B12">
+        <v>6.6</v>
+      </c>
+      <c r="C12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>555 days (Ind Green Product)</v>
+      </c>
+      <c r="B13">
+        <v>6.4</v>
+      </c>
+      <c r="C13">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2 years to less than 3 years</v>
+      </c>
+      <c r="B14">
+        <v>6.15</v>
+      </c>
+      <c r="C14">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3 years to less than 5 years</v>
+      </c>
+      <c r="B15">
+        <v>6.05</v>
+      </c>
+      <c r="C15">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C13"/>
   <cols>
@@ -1386,7 +1792,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
         <v>3.5</v>
@@ -1397,535 +1803,128 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>46 days to 90 days</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>07-30 days</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31-45 days</v>
-      </c>
-      <c r="B3">
-        <v>3.15</v>
-      </c>
-      <c r="C3">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46- 60 days</v>
-      </c>
-      <c r="B4">
-        <v>4.35</v>
-      </c>
-      <c r="C4">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>61- 90 days</v>
-      </c>
-      <c r="B5">
-        <v>4.6</v>
-      </c>
-      <c r="C5">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 days to 6 months</v>
-      </c>
-      <c r="B6">
-        <v>5.35</v>
-      </c>
-      <c r="C6">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months 1 day to 270 Days</v>
-      </c>
-      <c r="B7">
-        <v>5.5</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to &lt; 1 year</v>
-      </c>
-      <c r="B8">
-        <v>5.8</v>
-      </c>
-      <c r="C8">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 Year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">&gt;1 Year to 2 Years
-(except 555 days &amp; 700 Days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>&gt; 2 Years to &lt;3years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years to &lt;5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.35</v>
-      </c>
-      <c r="C12">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>&gt;5 years to 7 years</v>
-      </c>
-      <c r="B14">
-        <v>5.95</v>
-      </c>
-      <c r="C14">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>&gt;7 years to 10 years</v>
-      </c>
-      <c r="B15">
-        <v>5.9</v>
-      </c>
-      <c r="C15">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>&gt;10 years to 20 years$</v>
-      </c>
-      <c r="B16">
-        <v>4.8</v>
-      </c>
-      <c r="C16">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>1111 Days</v>
-      </c>
-      <c r="B17">
-        <v>6.35</v>
-      </c>
-      <c r="C17">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>370 Days</v>
-      </c>
-      <c r="B18">
-        <v>6.1</v>
-      </c>
-      <c r="C18">
-        <v>6.1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 to 14 days</v>
-      </c>
-      <c r="B2">
-        <v>2.8</v>
-      </c>
-      <c r="C2">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 to 29 days</v>
-      </c>
-      <c r="B3">
-        <v>2.8</v>
-      </c>
-      <c r="C3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>30 to 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 to 90 days</v>
-      </c>
-      <c r="B5">
-        <v>3.25</v>
-      </c>
-      <c r="C5">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 to 120 days</v>
-      </c>
-      <c r="B6">
-        <v>3.5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>121 to 180 days</v>
-      </c>
-      <c r="B7">
-        <v>3.85</v>
-      </c>
-      <c r="C7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>181 days to less than 9 months</v>
-      </c>
-      <c r="B8">
-        <v>4.5</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>9 months to less than 1 year</v>
-      </c>
-      <c r="B9">
-        <v>4.75</v>
-      </c>
-      <c r="C9">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B10">
-        <v>6.1</v>
-      </c>
-      <c r="C10">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 1 year to less than 2 years (Except 444 and 555 days)</v>
-      </c>
-      <c r="B11">
-        <v>6.2</v>
-      </c>
-      <c r="C11">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>444 days (Ind Secure Product)</v>
-      </c>
-      <c r="B12">
-        <v>6.6</v>
-      </c>
-      <c r="C12">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>555 days (Ind Green Product)</v>
-      </c>
-      <c r="B13">
-        <v>6.4</v>
-      </c>
-      <c r="C13">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2 years to less than 3 years</v>
-      </c>
-      <c r="B14">
-        <v>6.15</v>
-      </c>
-      <c r="C14">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>3 years to less than 5 years</v>
-      </c>
-      <c r="B15">
-        <v>6.05</v>
-      </c>
-      <c r="C15">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>6.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1952,134 +1951,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 - 14 days</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15-30 days</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 - 45 days</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>46 -59 days</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 - 90 days</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>91 -179 days</v>
+        <v>6 months - less than 1 year</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>180 -270 days</v>
+        <v>1 year</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>271-364 days</v>
+        <v>1 year 1 day - 1 year 9 months</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
+        <v>1 year 9 months 1 day - less than 2 years</v>
       </c>
       <c r="B10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
+        <v>2 years - less than 3 years</v>
       </c>
       <c r="B11">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
+        <v>3 years - less than 5 years</v>
       </c>
       <c r="B12">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C12">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
+        <v>5 years to up - 10 years</v>
       </c>
       <c r="B13">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="C13">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2091,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C6"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2111,139 +2110,62 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
-      </c>
-      <c r="B7">
-        <v>4.2</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
         <v>7.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>7.45</v>
-      </c>
-      <c r="C11">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>7.25</v>
-      </c>
-      <c r="C12">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
-      </c>
-      <c r="B13">
-        <v>5.85</v>
-      </c>
-      <c r="C13">
-        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2270,57 +2192,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>1 year</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>2 years</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>3 years</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>4 years</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>5 years</v>
       </c>
       <c r="B6">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="C6">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2469,88 +2391,6 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2 years</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3 years</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4 years</v>
-      </c>
-      <c r="B5">
-        <v>6.75</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5 years</v>
-      </c>
-      <c r="B6">
-        <v>6.75</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2940,231 +2780,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 Days</v>
-      </c>
-      <c r="B2">
-        <v>2.75</v>
-      </c>
-      <c r="C2">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15 - 30 Days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 Days</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 - 90 Days</v>
-      </c>
-      <c r="B5">
-        <v>3.5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>91 Days</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>92 Days - 179 Days</v>
-      </c>
-      <c r="B7">
-        <v>4.25</v>
-      </c>
-      <c r="C7">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 Days</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>181 Days to 269 Days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>270 Days</v>
-      </c>
-      <c r="B10">
-        <v>5.5</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>271 Days to 363 Days</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>364 Days</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>365 Days to less than 15 Months</v>
-      </c>
-      <c r="B13">
-        <v>6.35</v>
-      </c>
-      <c r="C13">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>15 Months - less than 18 Months</v>
-      </c>
-      <c r="B14">
-        <v>6.45</v>
-      </c>
-      <c r="C14">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>18 months - less than 2 years</v>
-      </c>
-      <c r="B15">
-        <v>6.55</v>
-      </c>
-      <c r="C15">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2 years- less than 3 years</v>
-      </c>
-      <c r="B16">
-        <v>6.65</v>
-      </c>
-      <c r="C16">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>3 years and above but less than 4 years</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4 years and above but less than 5 years</v>
-      </c>
-      <c r="B18">
-        <v>6.4</v>
-      </c>
-      <c r="C18">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>5 years and above upto and inclusive of 10 years</v>
-      </c>
-      <c r="B19">
-        <v>6.25</v>
-      </c>
-      <c r="C19">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3432,7 +3047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -3635,7 +3250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -3816,7 +3431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -3951,4 +3566,163 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 Days to 45 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 Days to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 Days to 179 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>180 Days to 269 Days</v>
+      </c>
+      <c r="B5">
+        <v>5.25</v>
+      </c>
+      <c r="C5">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>270 Days to less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+      </c>
+      <c r="B7">
+        <v>6.25</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>444 Days ##</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>555 Days ##</v>
+      </c>
+      <c r="B9">
+        <v>6.6</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years &amp; above to less than 3 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 Years &amp; above to less than 5 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 Years &amp; above to 10 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -7,22 +7,23 @@
     <sheet name="SBI" sheetId="2" r:id="rId2"/>
     <sheet name="ICICI Bank" sheetId="3" r:id="rId3"/>
     <sheet name="Axis Bank" sheetId="4" r:id="rId4"/>
-    <sheet name="PNB" sheetId="5" r:id="rId5"/>
-    <sheet name="IndusInd Bank" sheetId="6" r:id="rId6"/>
-    <sheet name="Yes Bank" sheetId="7" r:id="rId7"/>
-    <sheet name="IDFC First Bank" sheetId="8" r:id="rId8"/>
-    <sheet name="Canara Bank" sheetId="9" r:id="rId9"/>
-    <sheet name="Bank of Baroda" sheetId="10" r:id="rId10"/>
-    <sheet name="Bank of India" sheetId="11" r:id="rId11"/>
-    <sheet name="Bank of Maharashtra" sheetId="12" r:id="rId12"/>
-    <sheet name="RBL Bank" sheetId="13" r:id="rId13"/>
-    <sheet name="IDBI Bank" sheetId="14" r:id="rId14"/>
-    <sheet name="Indian Bank" sheetId="15" r:id="rId15"/>
-    <sheet name="Central Bank of India" sheetId="16" r:id="rId16"/>
-    <sheet name="Bandhan Bank" sheetId="17" r:id="rId17"/>
-    <sheet name="PNB Housing Finance" sheetId="18" r:id="rId18"/>
-    <sheet name="KTDFC" sheetId="19" r:id="rId19"/>
-    <sheet name="LIC Housing Finance" sheetId="20" r:id="rId20"/>
+    <sheet name="Kotak Mahindra Bank" sheetId="5" r:id="rId5"/>
+    <sheet name="PNB" sheetId="6" r:id="rId6"/>
+    <sheet name="IndusInd Bank" sheetId="7" r:id="rId7"/>
+    <sheet name="Yes Bank" sheetId="8" r:id="rId8"/>
+    <sheet name="IDFC First Bank" sheetId="9" r:id="rId9"/>
+    <sheet name="Canara Bank" sheetId="10" r:id="rId10"/>
+    <sheet name="Bank of Baroda" sheetId="11" r:id="rId11"/>
+    <sheet name="Bank of India" sheetId="12" r:id="rId12"/>
+    <sheet name="Bank of Maharashtra" sheetId="13" r:id="rId13"/>
+    <sheet name="RBL Bank" sheetId="14" r:id="rId14"/>
+    <sheet name="IDBI Bank" sheetId="15" r:id="rId15"/>
+    <sheet name="Indian Bank" sheetId="16" r:id="rId16"/>
+    <sheet name="Central Bank of India" sheetId="17" r:id="rId17"/>
+    <sheet name="Bandhan Bank" sheetId="18" r:id="rId18"/>
+    <sheet name="PNB Housing Finance" sheetId="19" r:id="rId19"/>
+    <sheet name="KTDFC" sheetId="20" r:id="rId20"/>
+    <sheet name="LIC Housing Finance" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -652,6 +653,165 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 Days to 45 Days*</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>46 Days to 90 Days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>91 Days to 179 Days</v>
+      </c>
+      <c r="B4">
+        <v>4.25</v>
+      </c>
+      <c r="C4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>180 Days to 269 Days</v>
+      </c>
+      <c r="B5">
+        <v>5.25</v>
+      </c>
+      <c r="C5">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>270 Days to less than 1 Year</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
+      </c>
+      <c r="B7">
+        <v>6.25</v>
+      </c>
+      <c r="C7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>444 Days ##</v>
+      </c>
+      <c r="B8">
+        <v>6.5</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>555 Days ##</v>
+      </c>
+      <c r="B9">
+        <v>6.6</v>
+      </c>
+      <c r="C9">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
+      </c>
+      <c r="B10">
+        <v>6.25</v>
+      </c>
+      <c r="C10">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 Years &amp; above to less than 3 Years</v>
+      </c>
+      <c r="B11">
+        <v>6.25</v>
+      </c>
+      <c r="C11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 Years &amp; above to less than 5 Years</v>
+      </c>
+      <c r="B12">
+        <v>6.25</v>
+      </c>
+      <c r="C12">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 Years &amp; above to 10 Years</v>
+      </c>
+      <c r="B13">
+        <v>6.25</v>
+      </c>
+      <c r="C13">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -853,7 +1013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1041,165 +1201,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 days to 30 days</v>
-      </c>
-      <c r="B2">
-        <v>2.6</v>
-      </c>
-      <c r="C2">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>31 days to 45 days</v>
-      </c>
-      <c r="B3">
-        <v>2.75</v>
-      </c>
-      <c r="C3">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>46 days to 90 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>91 days to 119 days</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>120 days to 180 days</v>
-      </c>
-      <c r="B6">
-        <v>4.75</v>
-      </c>
-      <c r="C6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>181 days to 270 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>271 days to 364 days</v>
-      </c>
-      <c r="B8">
-        <v>5.25</v>
-      </c>
-      <c r="C8">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>1 year</v>
-      </c>
-      <c r="B9">
-        <v>6.2</v>
-      </c>
-      <c r="C9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 year to 2 years</v>
-      </c>
-      <c r="B10">
-        <v>6.15</v>
-      </c>
-      <c r="C10">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Above 2 years to 3 years</v>
-      </c>
-      <c r="B11">
-        <v>5.25</v>
-      </c>
-      <c r="C11">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Above3 years to 5 years</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Above 5 years</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1226,24 +1227,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days to 14 days</v>
+        <v>7 days to 30 days</v>
       </c>
       <c r="B2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days to 45 days</v>
+        <v>31 days to 45 days</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -1251,109 +1252,109 @@
         <v>46 days to 90 days</v>
       </c>
       <c r="B4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>91 days to 180 days</v>
+        <v>91 days to 119 days</v>
       </c>
       <c r="B5">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>181 days to 240 days</v>
+        <v>120 days to 180 days</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>241 days to 364 days</v>
+        <v>181 days to 270 days</v>
       </c>
       <c r="B7">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>365 days to (12 months) 500 days</v>
+        <v>271 days to 364 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>501 days to less than 18 months)</v>
+        <v>1 year</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>18 months to 24 months</v>
+        <v>Above 1 year to 2 years</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>24 months 1 day to 36 months</v>
+        <v>Above 2 years to 3 years</v>
       </c>
       <c r="B11">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="C11">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>36 months 1 day to 60 months</v>
+        <v>Above3 years to 5 years</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>60 months to 120 months</v>
+        <v>Above 5 years</v>
       </c>
       <c r="B13">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
@@ -1364,6 +1365,165 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 days to 14 days</v>
+      </c>
+      <c r="B2">
+        <v>3.5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 days to 45 days</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>46 days to 90 days</v>
+      </c>
+      <c r="B4">
+        <v>4.5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>91 days to 180 days</v>
+      </c>
+      <c r="B5">
+        <v>4.75</v>
+      </c>
+      <c r="C5">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>181 days to 240 days</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>241 days to 364 days</v>
+      </c>
+      <c r="B7">
+        <v>6.05</v>
+      </c>
+      <c r="C7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>365 days to (12 months) 500 days</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>501 days to less than 18 months)</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>18 months to 24 months</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>24 months 1 day to 36 months</v>
+      </c>
+      <c r="B11">
+        <v>7.2</v>
+      </c>
+      <c r="C11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36 months 1 day to 60 months</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>60 months to 120 months</v>
+      </c>
+      <c r="B13">
+        <v>6.7</v>
+      </c>
+      <c r="C13">
+        <v>7.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>
@@ -1578,7 +1738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C16"/>
   <cols>
@@ -1766,165 +1926,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 - 14 days</v>
-      </c>
-      <c r="B2">
-        <v>3.5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>15-30 days</v>
-      </c>
-      <c r="B3">
-        <v>3.75</v>
-      </c>
-      <c r="C3">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>31 - 45 days</v>
-      </c>
-      <c r="B4">
-        <v>3.75</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>46 -59 days</v>
-      </c>
-      <c r="B5">
-        <v>4.5</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>60 - 90 days</v>
-      </c>
-      <c r="B6">
-        <v>4.5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>91 -179 days</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>180 -270 days</v>
-      </c>
-      <c r="B8">
-        <v>5.5</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>271-364 days</v>
-      </c>
-      <c r="B9">
-        <v>5.5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>1 yr to less than 2 yrs</v>
-      </c>
-      <c r="B10">
-        <v>6.4</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 yr to less than 3 years</v>
-      </c>
-      <c r="B11">
-        <v>6.5</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 yr to less than 5 years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 years &amp; above up to 10 years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1951,134 +1952,134 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>7 days - 14 days</v>
+        <v>7 - 14 days</v>
       </c>
       <c r="B2">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>15 days - 30 days</v>
+        <v>15-30 days</v>
       </c>
       <c r="B3">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="C3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>31 days - less than 2 months</v>
+        <v>31 - 45 days</v>
       </c>
       <c r="B4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="C4">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2 months - less than 3 months</v>
+        <v>46 -59 days</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C5">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3 months - less than 6 months</v>
+        <v>60 - 90 days</v>
       </c>
       <c r="B6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C6">
-        <v>4.95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6 months - less than 1 year</v>
+        <v>91 -179 days</v>
       </c>
       <c r="B7">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1 year</v>
+        <v>180 -270 days</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1 year 1 day - 1 year 9 months</v>
+        <v>271-364 days</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1 year 9 months 1 day - less than 2 years</v>
+        <v>1 yr to less than 2 yrs</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2 years - less than 3 years</v>
+        <v>2 yr to less than 3 years</v>
       </c>
       <c r="B11">
-        <v>7.45</v>
+        <v>6.5</v>
       </c>
       <c r="C11">
-        <v>7.95</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>3 years - less than 5 years</v>
+        <v>3 yr to less than 5 years</v>
       </c>
       <c r="B12">
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="C12">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5 years to up - 10 years</v>
+        <v>5 years &amp; above up to 10 years</v>
       </c>
       <c r="B13">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="C13">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2091,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C13"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -2110,62 +2111,139 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12 months - 23 months</v>
+        <v>7 days - 14 days</v>
       </c>
       <c r="B2">
-        <v>6.7</v>
+        <v>2.95</v>
       </c>
       <c r="C2">
-        <v>6.95</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>24 months - 35 months</v>
+        <v>15 days - 30 days</v>
       </c>
       <c r="B3">
-        <v>6.85</v>
+        <v>2.95</v>
       </c>
       <c r="C3">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>36 months - 47 months</v>
+        <v>31 days - less than 2 months</v>
       </c>
       <c r="B4">
-        <v>7.1</v>
+        <v>3.45</v>
       </c>
       <c r="C4">
-        <v>7.35</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>48 months - 59 months</v>
+        <v>2 months - less than 3 months</v>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>7.35</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>60 months</v>
+        <v>3 months - less than 6 months</v>
       </c>
       <c r="B6">
+        <v>4.2</v>
+      </c>
+      <c r="C6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6 months - less than 1 year</v>
+      </c>
+      <c r="B7">
+        <v>4.2</v>
+      </c>
+      <c r="C7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1 year 1 day - 1 year 9 months</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1 year 9 months 1 day - less than 2 years</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2 years - less than 3 years</v>
+      </c>
+      <c r="B11">
+        <v>7.45</v>
+      </c>
+      <c r="C11">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3 years - less than 5 years</v>
+      </c>
+      <c r="B12">
         <v>7.25</v>
       </c>
-      <c r="C6">
-        <v>7.5</v>
+      <c r="C12">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5 years to up - 10 years</v>
+      </c>
+      <c r="B13">
+        <v>5.85</v>
+      </c>
+      <c r="C13">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2192,57 +2270,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1 year</v>
+        <v>12 months - 23 months</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="C2">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2 years</v>
+        <v>24 months - 35 months</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="C3">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3 years</v>
+        <v>36 months - 47 months</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="C4">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4 years</v>
+        <v>48 months - 59 months</v>
       </c>
       <c r="B5">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5 years</v>
+        <v>60 months</v>
       </c>
       <c r="B6">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -2391,6 +2469,88 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 year</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 years</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 years</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 years</v>
+      </c>
+      <c r="B5">
+        <v>6.75</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5 years</v>
+      </c>
+      <c r="B6">
+        <v>6.75</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -2780,6 +2940,231 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tenure</v>
+      </c>
+      <c r="B1" t="str">
+        <v>General Rate (%)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Senior Citizen Rate (%)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>7 - 14 Days</v>
+      </c>
+      <c r="B2">
+        <v>2.75</v>
+      </c>
+      <c r="C2">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>15 - 30 Days</v>
+      </c>
+      <c r="B3">
+        <v>2.75</v>
+      </c>
+      <c r="C3">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>31 - 45 Days</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>46 - 90 Days</v>
+      </c>
+      <c r="B5">
+        <v>3.5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>91 Days</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>92 Days - 179 Days</v>
+      </c>
+      <c r="B7">
+        <v>4.25</v>
+      </c>
+      <c r="C7">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>180 Days</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>181 Days to 269 Days</v>
+      </c>
+      <c r="B9">
+        <v>5.5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>270 Days</v>
+      </c>
+      <c r="B10">
+        <v>5.5</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>271 Days to 363 Days</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>364 Days</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>365 Days to less than 15 Months</v>
+      </c>
+      <c r="B13">
+        <v>6.35</v>
+      </c>
+      <c r="C13">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>15 Months - less than 18 Months</v>
+      </c>
+      <c r="B14">
+        <v>6.45</v>
+      </c>
+      <c r="C14">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>18 months - less than 2 years</v>
+      </c>
+      <c r="B15">
+        <v>6.55</v>
+      </c>
+      <c r="C15">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2 years- less than 3 years</v>
+      </c>
+      <c r="B16">
+        <v>6.65</v>
+      </c>
+      <c r="C16">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>3 years and above but less than 4 years</v>
+      </c>
+      <c r="B17">
+        <v>6.4</v>
+      </c>
+      <c r="C17">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4 years and above but less than 5 years</v>
+      </c>
+      <c r="B18">
+        <v>6.4</v>
+      </c>
+      <c r="C18">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>5 years and above upto and inclusive of 10 years</v>
+      </c>
+      <c r="B19">
+        <v>6.25</v>
+      </c>
+      <c r="C19">
+        <v>6.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C23"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
@@ -3047,7 +3432,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C17"/>
   <cols>
@@ -3250,7 +3635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C15"/>
   <cols>
@@ -3431,7 +3816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <cols>
@@ -3566,163 +3951,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Tenure</v>
-      </c>
-      <c r="B1" t="str">
-        <v>General Rate (%)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Senior Citizen Rate (%)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>7 Days to 45 Days*</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>46 Days to 90 Days</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>91 Days to 179 Days</v>
-      </c>
-      <c r="B4">
-        <v>4.25</v>
-      </c>
-      <c r="C4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>180 Days to 269 Days</v>
-      </c>
-      <c r="B5">
-        <v>5.25</v>
-      </c>
-      <c r="C5">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>270 Days to less than 1 Year</v>
-      </c>
-      <c r="B6">
-        <v>5.5</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>1 Year &amp; above to 1 year 3 months Only (Except 444 days)</v>
-      </c>
-      <c r="B7">
-        <v>6.25</v>
-      </c>
-      <c r="C7">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>444 Days ##</v>
-      </c>
-      <c r="B8">
-        <v>6.5</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>555 Days ##</v>
-      </c>
-      <c r="B9">
-        <v>6.6</v>
-      </c>
-      <c r="C9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Above 1 Year 3 months to less than 2 Years (Except 555 days)</v>
-      </c>
-      <c r="B10">
-        <v>6.25</v>
-      </c>
-      <c r="C10">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2 Years &amp; above to less than 3 Years</v>
-      </c>
-      <c r="B11">
-        <v>6.25</v>
-      </c>
-      <c r="C11">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>3 Years &amp; above to less than 5 Years</v>
-      </c>
-      <c r="B12">
-        <v>6.25</v>
-      </c>
-      <c r="C12">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>5 Years &amp; above to 10 Years</v>
-      </c>
-      <c r="B13">
-        <v>6.25</v>
-      </c>
-      <c r="C13">
-        <v>6.75</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -2443,10 +2443,10 @@
         <v>1 Year</v>
       </c>
       <c r="B10">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="C10">
-        <v>7.05</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
@@ -2454,10 +2454,10 @@
         <v>2 Years</v>
       </c>
       <c r="B11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="C11">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -2678,10 +2678,10 @@
         <v>2 Years 1 Day to 3 Years</v>
       </c>
       <c r="B8">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="C8">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="9">
@@ -2689,10 +2689,10 @@
         <v>3 Years 1 Day to 5 Years</v>
       </c>
       <c r="B9">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C9">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="10">
@@ -2700,10 +2700,10 @@
         <v>5 Years 1 Day to 10 Years</v>
       </c>
       <c r="B10">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -3084,10 +3084,10 @@
         <v>365 Days to less than 15 Months</v>
       </c>
       <c r="B13">
-        <v>6.35</v>
+        <v>6.45</v>
       </c>
       <c r="C13">
-        <v>6.85</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="14">
@@ -3117,10 +3117,10 @@
         <v>2 years- less than 3 years</v>
       </c>
       <c r="B16">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
       <c r="C16">
-        <v>7.15</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="17">

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -2735,7 +2735,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>14 days</v>
+        <v>7 – 14 days</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>29 days</v>
+        <v>15 – 29 days</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>45 days</v>
+        <v>30 – 45 days</v>
       </c>
       <c r="B4">
         <v>3.25</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>60 days</v>
+        <v>46 – 60 days</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>24 days</v>
+        <v>88 days – 3 months 24 days</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -2801,7 +2801,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>25 days &lt; 4 months</v>
+        <v>3 months 25 days &lt; 4 months</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>10 days</v>
+        <v>1 year – 1 year 10 days</v>
       </c>
       <c r="B12">
         <v>6.25</v>
@@ -2856,7 +2856,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>11 days &lt; 13 months</v>
+        <v>1 year 11 days &lt; 13 months</v>
       </c>
       <c r="B13">
         <v>6.25</v>
@@ -2903,10 +2903,10 @@
         <v>2 years &lt; 3 years</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="18">
@@ -2914,10 +2914,10 @@
         <v>3 years &lt; 5 years</v>
       </c>
       <c r="B18">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="19">
@@ -2925,10 +2925,10 @@
         <v>5 years to 10 years</v>
       </c>
       <c r="B19">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C19">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/FD_Rates.xlsx
+++ b/output/FD_Rates.xlsx
@@ -3600,10 +3600,10 @@
         <v>2 Years to 3 Years</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="C15">
-        <v>7.75</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="16">
